--- a/1_lecturas/inputs/registro_operario_acumulado.xlsx
+++ b/1_lecturas/inputs/registro_operario_acumulado.xlsx
@@ -5263,7 +5263,7 @@
       </c>
       <c r="C141" s="8" t="inlineStr">
         <is>
-          <t>RODRIGO SAAVEDRA TRUJILLO</t>
+          <t>RODRIGO TRUJILLO SAAVEDRA</t>
         </is>
       </c>
       <c r="D141" s="7" t="n"/>
@@ -9277,7 +9277,7 @@
       </c>
       <c r="C261" s="8" t="inlineStr">
         <is>
-          <t>IGLESIA EVANGELICA BAUTISTA</t>
+          <t>RAMON REQUEZ MENDOZA</t>
         </is>
       </c>
       <c r="D261" s="7" t="n"/>
@@ -18499,7 +18499,7 @@
       </c>
       <c r="C539" s="8" t="inlineStr">
         <is>
-          <t>EFRAIN CANDACHO HUARAC</t>
+          <t>CESAR ALFREDO VIRU GASPAR</t>
         </is>
       </c>
       <c r="D539" s="7" t="n"/>
@@ -18533,7 +18533,7 @@
       </c>
       <c r="C540" s="8" t="inlineStr">
         <is>
-          <t>CESAR ALFREDO VIRU GASPAR</t>
+          <t>EFRAIN CANDACHO HUARAC</t>
         </is>
       </c>
       <c r="D540" s="7" t="n"/>

--- a/1_lecturas/inputs/registro_operario_acumulado.xlsx
+++ b/1_lecturas/inputs/registro_operario_acumulado.xlsx
@@ -571,7 +571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L578"/>
+  <dimension ref="A1:N578"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -586,6 +586,8 @@
     <col width="8" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
     <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -627,12 +629,18 @@
         </is>
       </c>
       <c r="J1" s="3" t="n"/>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
       <c r="L1" s="3" t="n"/>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="5" t="n"/>
@@ -679,6 +687,16 @@
           <t>M3</t>
         </is>
       </c>
+      <c r="M2" s="6" t="inlineStr">
+        <is>
+          <t>MARCACION</t>
+        </is>
+      </c>
+      <c r="N2" s="6" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
@@ -719,6 +737,12 @@
       <c r="L3" s="9" t="n">
         <v>8</v>
       </c>
+      <c r="M3" s="9" t="n">
+        <v>52</v>
+      </c>
+      <c r="N3" s="9" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
@@ -759,6 +783,12 @@
       <c r="L4" s="9" t="n">
         <v>21</v>
       </c>
+      <c r="M4" s="9" t="n">
+        <v>2806</v>
+      </c>
+      <c r="N4" s="9" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
@@ -799,6 +829,12 @@
       <c r="L5" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M5" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="N5" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
@@ -839,6 +875,12 @@
       <c r="L6" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M6" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="N6" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
@@ -878,6 +920,12 @@
       </c>
       <c r="L7" s="9" t="n">
         <v>16</v>
+      </c>
+      <c r="M7" s="9" t="n">
+        <v>98</v>
+      </c>
+      <c r="N7" s="9" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
@@ -909,6 +957,8 @@
       <c r="L8" s="9" t="n">
         <v>0</v>
       </c>
+      <c r="M8" s="9" t="n"/>
+      <c r="N8" s="9" t="n"/>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
@@ -948,6 +998,12 @@
       </c>
       <c r="L9" s="9" t="n">
         <v>24</v>
+      </c>
+      <c r="M9" s="9" t="n">
+        <v>173</v>
+      </c>
+      <c r="N9" s="9" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
@@ -979,6 +1035,8 @@
       <c r="J10" s="9" t="n"/>
       <c r="K10" s="9" t="n"/>
       <c r="L10" s="9" t="n"/>
+      <c r="M10" s="9" t="n"/>
+      <c r="N10" s="9" t="n"/>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
@@ -1019,6 +1077,12 @@
       <c r="L11" s="9" t="n">
         <v>7</v>
       </c>
+      <c r="M11" s="9" t="n">
+        <v>1811</v>
+      </c>
+      <c r="N11" s="9" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
@@ -1059,6 +1123,12 @@
       <c r="L12" s="9" t="n">
         <v>16</v>
       </c>
+      <c r="M12" s="9" t="n">
+        <v>126</v>
+      </c>
+      <c r="N12" s="9" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
@@ -1099,6 +1169,12 @@
       <c r="L13" s="9" t="n">
         <v>10</v>
       </c>
+      <c r="M13" s="9" t="n">
+        <v>252</v>
+      </c>
+      <c r="N13" s="9" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" s="7" t="inlineStr">
@@ -1134,10 +1210,16 @@
         <v>33</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>2403</v>
+        <v>2574</v>
       </c>
       <c r="L14" s="9" t="n">
         <v>30</v>
+      </c>
+      <c r="M14" s="9" t="n">
+        <v>2618</v>
+      </c>
+      <c r="N14" s="9" t="n">
+        <v>44</v>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
@@ -1178,6 +1260,12 @@
       </c>
       <c r="L15" s="9" t="n">
         <v>11</v>
+      </c>
+      <c r="M15" s="9" t="n">
+        <v>740</v>
+      </c>
+      <c r="N15" s="9" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
@@ -1213,6 +1301,8 @@
       <c r="J16" s="9" t="n"/>
       <c r="K16" s="9" t="n"/>
       <c r="L16" s="9" t="n"/>
+      <c r="M16" s="9" t="n"/>
+      <c r="N16" s="9" t="n"/>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
@@ -1253,6 +1343,12 @@
       <c r="L17" s="9" t="n">
         <v>15</v>
       </c>
+      <c r="M17" s="9" t="n">
+        <v>392</v>
+      </c>
+      <c r="N17" s="9" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" s="7" t="inlineStr">
@@ -1293,6 +1389,12 @@
       <c r="L18" s="9" t="n">
         <v>12</v>
       </c>
+      <c r="M18" s="9" t="n">
+        <v>64</v>
+      </c>
+      <c r="N18" s="9" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
@@ -1333,6 +1435,12 @@
       <c r="L19" s="9" t="n">
         <v>11</v>
       </c>
+      <c r="M19" s="9" t="n">
+        <v>67</v>
+      </c>
+      <c r="N19" s="9" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" s="7" t="inlineStr">
@@ -1373,6 +1481,12 @@
       <c r="L20" s="9" t="n">
         <v>8</v>
       </c>
+      <c r="M20" s="9" t="n">
+        <v>879</v>
+      </c>
+      <c r="N20" s="9" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" s="7" t="inlineStr">
@@ -1413,6 +1527,12 @@
       <c r="L21" s="9" t="n">
         <v>23</v>
       </c>
+      <c r="M21" s="9" t="n">
+        <v>723</v>
+      </c>
+      <c r="N21" s="9" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" s="7" t="inlineStr">
@@ -1453,6 +1573,12 @@
       <c r="L22" s="9" t="n">
         <v>30</v>
       </c>
+      <c r="M22" s="9" t="n">
+        <v>266</v>
+      </c>
+      <c r="N22" s="9" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" s="7" t="inlineStr">
@@ -1493,6 +1619,12 @@
       <c r="L23" s="9" t="n">
         <v>20</v>
       </c>
+      <c r="M23" s="9" t="n">
+        <v>146</v>
+      </c>
+      <c r="N23" s="9" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" s="7" t="inlineStr">
@@ -1528,10 +1660,16 @@
         <v>14</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>81</v>
+        <v>53</v>
       </c>
       <c r="L24" s="9" t="n">
         <v>18</v>
+      </c>
+      <c r="M24" s="9" t="n">
+        <v>77</v>
+      </c>
+      <c r="N24" s="9" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
@@ -1573,6 +1711,12 @@
       <c r="L25" s="9" t="n">
         <v>21</v>
       </c>
+      <c r="M25" s="9" t="n">
+        <v>93</v>
+      </c>
+      <c r="N25" s="9" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" s="7" t="inlineStr">
@@ -1608,9 +1752,15 @@
         <v>14</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>5</v>
+        <v>89</v>
       </c>
       <c r="L26" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="M26" s="9" t="n">
+        <v>91</v>
+      </c>
+      <c r="N26" s="9" t="n">
         <v>5</v>
       </c>
     </row>
@@ -1653,6 +1803,12 @@
       <c r="L27" s="9" t="n">
         <v>6</v>
       </c>
+      <c r="M27" s="9" t="n">
+        <v>466</v>
+      </c>
+      <c r="N27" s="9" t="n">
+        <v>27</v>
+      </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" s="7" t="inlineStr">
@@ -1693,6 +1849,12 @@
       <c r="L28" s="9" t="n">
         <v>17</v>
       </c>
+      <c r="M28" s="9" t="n">
+        <v>113</v>
+      </c>
+      <c r="N28" s="9" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" s="7" t="inlineStr">
@@ -1733,6 +1895,12 @@
       <c r="L29" s="9" t="n">
         <v>6</v>
       </c>
+      <c r="M29" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="N29" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" s="7" t="inlineStr">
@@ -1773,6 +1941,12 @@
       <c r="L30" s="9" t="n">
         <v>7</v>
       </c>
+      <c r="M30" s="9" t="n">
+        <v>394</v>
+      </c>
+      <c r="N30" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" s="7" t="inlineStr">
@@ -1813,6 +1987,12 @@
       <c r="L31" s="9" t="n">
         <v>9</v>
       </c>
+      <c r="M31" s="9" t="n">
+        <v>332</v>
+      </c>
+      <c r="N31" s="9" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" s="7" t="inlineStr">
@@ -1852,6 +2032,12 @@
       </c>
       <c r="L32" s="9" t="n">
         <v>5</v>
+      </c>
+      <c r="M32" s="9" t="n">
+        <v>237</v>
+      </c>
+      <c r="N32" s="9" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
@@ -1883,6 +2069,8 @@
       <c r="J33" s="9" t="n"/>
       <c r="K33" s="9" t="n"/>
       <c r="L33" s="9" t="n"/>
+      <c r="M33" s="9" t="n"/>
+      <c r="N33" s="9" t="n"/>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" s="7" t="inlineStr">
@@ -1923,6 +2111,12 @@
       <c r="L34" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M34" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="N34" s="9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" s="7" t="inlineStr">
@@ -1963,6 +2157,12 @@
       <c r="L35" s="9" t="n">
         <v>22</v>
       </c>
+      <c r="M35" s="9" t="n">
+        <v>1212</v>
+      </c>
+      <c r="N35" s="9" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" s="7" t="inlineStr">
@@ -2003,6 +2203,12 @@
       <c r="L36" s="9" t="n">
         <v>6</v>
       </c>
+      <c r="M36" s="9" t="n">
+        <v>608</v>
+      </c>
+      <c r="N36" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" s="7" t="inlineStr">
@@ -2043,6 +2249,12 @@
       <c r="L37" s="9" t="n">
         <v>7</v>
       </c>
+      <c r="M37" s="9" t="n">
+        <v>1356</v>
+      </c>
+      <c r="N37" s="9" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" s="7" t="inlineStr">
@@ -2083,6 +2295,12 @@
       <c r="L38" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M38" s="9" t="n">
+        <v>213</v>
+      </c>
+      <c r="N38" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" s="7" t="inlineStr">
@@ -2123,6 +2341,12 @@
       <c r="L39" s="9" t="n">
         <v>16</v>
       </c>
+      <c r="M39" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="N39" s="9" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" s="7" t="inlineStr">
@@ -2161,6 +2385,12 @@
         <v>23</v>
       </c>
       <c r="L40" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="M40" s="9" t="n">
+        <v>26</v>
+      </c>
+      <c r="N40" s="9" t="n">
         <v>5</v>
       </c>
     </row>
@@ -2192,9 +2422,15 @@
       <c r="I41" s="9" t="n"/>
       <c r="J41" s="9" t="n"/>
       <c r="K41" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L41" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="M41" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" s="9" t="n">
         <v>5</v>
       </c>
     </row>
@@ -2237,6 +2473,12 @@
       <c r="L42" s="9" t="n">
         <v>7</v>
       </c>
+      <c r="M42" s="9" t="n">
+        <v>739</v>
+      </c>
+      <c r="N42" s="9" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" s="7" t="inlineStr">
@@ -2277,6 +2519,12 @@
       <c r="L43" s="9" t="n">
         <v>9</v>
       </c>
+      <c r="M43" s="9" t="n">
+        <v>82</v>
+      </c>
+      <c r="N43" s="9" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" s="7" t="inlineStr">
@@ -2317,6 +2565,12 @@
       <c r="L44" s="9" t="n">
         <v>19</v>
       </c>
+      <c r="M44" s="9" t="n">
+        <v>117</v>
+      </c>
+      <c r="N44" s="9" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" s="7" t="inlineStr">
@@ -2357,6 +2611,12 @@
       <c r="L45" s="9" t="n">
         <v>7</v>
       </c>
+      <c r="M45" s="9" t="n">
+        <v>632</v>
+      </c>
+      <c r="N45" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" s="7" t="inlineStr">
@@ -2397,6 +2657,12 @@
       <c r="L46" s="9" t="n">
         <v>16</v>
       </c>
+      <c r="M46" s="9" t="n">
+        <v>158</v>
+      </c>
+      <c r="N46" s="9" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" s="7" t="inlineStr">
@@ -2437,6 +2703,12 @@
       <c r="L47" s="9" t="n">
         <v>6</v>
       </c>
+      <c r="M47" s="9" t="n">
+        <v>320</v>
+      </c>
+      <c r="N47" s="9" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="48" ht="15" customHeight="1">
       <c r="A48" s="7" t="inlineStr">
@@ -2477,6 +2749,12 @@
       <c r="L48" s="9" t="n">
         <v>19</v>
       </c>
+      <c r="M48" s="9" t="n">
+        <v>1111</v>
+      </c>
+      <c r="N48" s="9" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="49" ht="15" customHeight="1">
       <c r="A49" s="7" t="inlineStr">
@@ -2517,6 +2795,12 @@
       <c r="L49" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M49" s="9" t="n">
+        <v>2175</v>
+      </c>
+      <c r="N49" s="9" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="50" ht="15" customHeight="1">
       <c r="A50" s="7" t="inlineStr">
@@ -2556,6 +2840,12 @@
       </c>
       <c r="L50" s="9" t="n">
         <v>8</v>
+      </c>
+      <c r="M50" s="9" t="n">
+        <v>561</v>
+      </c>
+      <c r="N50" s="9" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1">
@@ -2586,9 +2876,15 @@
       <c r="I51" s="9" t="n"/>
       <c r="J51" s="9" t="n"/>
       <c r="K51" s="9" t="n">
-        <v>15</v>
+        <v>1117</v>
       </c>
       <c r="L51" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="M51" s="9" t="n">
+        <v>1117</v>
+      </c>
+      <c r="N51" s="9" t="n">
         <v>5</v>
       </c>
     </row>
@@ -2631,6 +2927,12 @@
       <c r="L52" s="9" t="n">
         <v>14</v>
       </c>
+      <c r="M52" s="9" t="n">
+        <v>926</v>
+      </c>
+      <c r="N52" s="9" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="53" ht="15" customHeight="1">
       <c r="A53" s="7" t="inlineStr">
@@ -2671,6 +2973,12 @@
       <c r="L53" s="9" t="n">
         <v>13</v>
       </c>
+      <c r="M53" s="9" t="n">
+        <v>1756</v>
+      </c>
+      <c r="N53" s="9" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="54" ht="15" customHeight="1">
       <c r="A54" s="7" t="inlineStr">
@@ -2711,6 +3019,12 @@
       <c r="L54" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M54" s="9" t="n">
+        <v>46</v>
+      </c>
+      <c r="N54" s="9" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="55" ht="15" customHeight="1">
       <c r="A55" s="7" t="inlineStr">
@@ -2751,6 +3065,12 @@
       <c r="L55" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M55" s="9" t="n">
+        <v>44</v>
+      </c>
+      <c r="N55" s="9" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="56" ht="15" customHeight="1">
       <c r="A56" s="7" t="inlineStr">
@@ -2791,6 +3111,12 @@
       <c r="L56" s="9" t="n">
         <v>10</v>
       </c>
+      <c r="M56" s="9" t="n">
+        <v>187</v>
+      </c>
+      <c r="N56" s="9" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="57" ht="15" customHeight="1">
       <c r="A57" s="7" t="inlineStr">
@@ -2829,6 +3155,12 @@
         <v>68</v>
       </c>
       <c r="L57" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="M57" s="9" t="n">
+        <v>73</v>
+      </c>
+      <c r="N57" s="9" t="n">
         <v>5</v>
       </c>
     </row>
@@ -2860,9 +3192,15 @@
       <c r="I58" s="9" t="n"/>
       <c r="J58" s="9" t="n"/>
       <c r="K58" s="9" t="n">
-        <v>15</v>
+        <v>1240</v>
       </c>
       <c r="L58" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="M58" s="9" t="n">
+        <v>1241</v>
+      </c>
+      <c r="N58" s="9" t="n">
         <v>5</v>
       </c>
     </row>
@@ -2905,6 +3243,12 @@
       <c r="L59" s="9" t="n">
         <v>8</v>
       </c>
+      <c r="M59" s="9" t="n">
+        <v>49</v>
+      </c>
+      <c r="N59" s="9" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="60" ht="15" customHeight="1">
       <c r="A60" s="7" t="inlineStr">
@@ -2945,6 +3289,12 @@
       <c r="L60" s="9" t="n">
         <v>21</v>
       </c>
+      <c r="M60" s="9" t="n">
+        <v>165</v>
+      </c>
+      <c r="N60" s="9" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="61" ht="15" customHeight="1">
       <c r="A61" s="7" t="inlineStr">
@@ -2985,6 +3335,12 @@
       <c r="L61" s="9" t="n">
         <v>15</v>
       </c>
+      <c r="M61" s="9" t="n">
+        <v>104</v>
+      </c>
+      <c r="N61" s="9" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="62" ht="15" customHeight="1">
       <c r="A62" s="7" t="inlineStr">
@@ -3023,7 +3379,13 @@
         <v>1875</v>
       </c>
       <c r="L62" s="9" t="n">
-        <v>87</v>
+        <v>51</v>
+      </c>
+      <c r="M62" s="9" t="n">
+        <v>1926</v>
+      </c>
+      <c r="N62" s="9" t="n">
+        <v>51</v>
       </c>
     </row>
     <row r="63" ht="15" customHeight="1">
@@ -3065,6 +3427,12 @@
       <c r="L63" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M63" s="9" t="n">
+        <v>165</v>
+      </c>
+      <c r="N63" s="9" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="64" ht="15" customHeight="1">
       <c r="A64" s="7" t="inlineStr">
@@ -3105,6 +3473,12 @@
       <c r="L64" s="9" t="n">
         <v>18</v>
       </c>
+      <c r="M64" s="9" t="n">
+        <v>426</v>
+      </c>
+      <c r="N64" s="9" t="n">
+        <v>52</v>
+      </c>
     </row>
     <row r="65" ht="15" customHeight="1">
       <c r="A65" s="7" t="inlineStr">
@@ -3145,6 +3519,12 @@
       <c r="L65" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M65" s="9" t="n">
+        <v>556</v>
+      </c>
+      <c r="N65" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="66" ht="15" customHeight="1">
       <c r="A66" s="7" t="inlineStr">
@@ -3185,6 +3565,12 @@
       <c r="L66" s="9" t="n">
         <v>13</v>
       </c>
+      <c r="M66" s="9" t="n">
+        <v>98</v>
+      </c>
+      <c r="N66" s="9" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="67" ht="15" customHeight="1">
       <c r="A67" s="7" t="inlineStr">
@@ -3225,6 +3611,12 @@
       <c r="L67" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M67" s="9" t="n">
+        <v>1518</v>
+      </c>
+      <c r="N67" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="68" ht="15" customHeight="1">
       <c r="A68" s="7" t="inlineStr">
@@ -3264,6 +3656,12 @@
       </c>
       <c r="L68" s="9" t="n">
         <v>16</v>
+      </c>
+      <c r="M68" s="9" t="n">
+        <v>336</v>
+      </c>
+      <c r="N68" s="9" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1">
@@ -3295,6 +3693,8 @@
       <c r="J69" s="9" t="n"/>
       <c r="K69" s="9" t="n"/>
       <c r="L69" s="9" t="n"/>
+      <c r="M69" s="9" t="n"/>
+      <c r="N69" s="9" t="n"/>
     </row>
     <row r="70" ht="15" customHeight="1">
       <c r="A70" s="7" t="inlineStr">
@@ -3333,6 +3733,12 @@
         <v>147</v>
       </c>
       <c r="L70" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="M70" s="9" t="n">
+        <v>152</v>
+      </c>
+      <c r="N70" s="9" t="n">
         <v>5</v>
       </c>
     </row>
@@ -3365,6 +3771,8 @@
       <c r="J71" s="9" t="n"/>
       <c r="K71" s="9" t="n"/>
       <c r="L71" s="9" t="n"/>
+      <c r="M71" s="9" t="n"/>
+      <c r="N71" s="9" t="n"/>
     </row>
     <row r="72" ht="15" customHeight="1">
       <c r="A72" s="7" t="inlineStr">
@@ -3399,6 +3807,8 @@
       <c r="J72" s="9" t="n"/>
       <c r="K72" s="9" t="n"/>
       <c r="L72" s="9" t="n"/>
+      <c r="M72" s="9" t="n"/>
+      <c r="N72" s="9" t="n"/>
     </row>
     <row r="73" ht="15" customHeight="1">
       <c r="A73" s="7" t="inlineStr">
@@ -3439,6 +3849,12 @@
       <c r="L73" s="9" t="n">
         <v>20</v>
       </c>
+      <c r="M73" s="9" t="n">
+        <v>3693</v>
+      </c>
+      <c r="N73" s="9" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="74" ht="15" customHeight="1">
       <c r="A74" s="7" t="inlineStr">
@@ -3479,6 +3895,12 @@
       <c r="L74" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M74" s="9" t="n">
+        <v>26</v>
+      </c>
+      <c r="N74" s="9" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="75" ht="15" customHeight="1">
       <c r="A75" s="7" t="inlineStr">
@@ -3519,6 +3941,12 @@
       <c r="L75" s="9" t="n">
         <v>14</v>
       </c>
+      <c r="M75" s="9" t="n">
+        <v>418</v>
+      </c>
+      <c r="N75" s="9" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="76" ht="15" customHeight="1">
       <c r="A76" s="7" t="inlineStr">
@@ -3559,6 +3987,12 @@
       <c r="L76" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M76" s="9" t="n">
+        <v>44</v>
+      </c>
+      <c r="N76" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="77" ht="15" customHeight="1">
       <c r="A77" s="7" t="inlineStr">
@@ -3599,6 +4033,12 @@
       <c r="L77" s="9" t="n">
         <v>15</v>
       </c>
+      <c r="M77" s="9" t="n">
+        <v>715</v>
+      </c>
+      <c r="N77" s="9" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="78" ht="15" customHeight="1">
       <c r="A78" s="7" t="inlineStr">
@@ -3639,6 +4079,12 @@
       <c r="L78" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M78" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="N78" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="79" ht="15" customHeight="1">
       <c r="A79" s="7" t="inlineStr">
@@ -3678,6 +4124,12 @@
       </c>
       <c r="L79" s="9" t="n">
         <v>6</v>
+      </c>
+      <c r="M79" s="9" t="n">
+        <v>334</v>
+      </c>
+      <c r="N79" s="9" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1">
@@ -3709,6 +4161,8 @@
       <c r="J80" s="9" t="n"/>
       <c r="K80" s="9" t="n"/>
       <c r="L80" s="9" t="n"/>
+      <c r="M80" s="9" t="n"/>
+      <c r="N80" s="9" t="n"/>
     </row>
     <row r="81" ht="15" customHeight="1">
       <c r="A81" s="7" t="inlineStr">
@@ -3749,6 +4203,12 @@
       <c r="L81" s="9" t="n">
         <v>15</v>
       </c>
+      <c r="M81" s="9" t="n">
+        <v>393</v>
+      </c>
+      <c r="N81" s="9" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="82" ht="15" customHeight="1">
       <c r="A82" s="7" t="inlineStr">
@@ -3787,6 +4247,12 @@
         <v>8</v>
       </c>
       <c r="L82" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="M82" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="N82" s="9" t="n">
         <v>5</v>
       </c>
     </row>
@@ -3819,6 +4285,8 @@
       <c r="J83" s="9" t="n"/>
       <c r="K83" s="9" t="n"/>
       <c r="L83" s="9" t="n"/>
+      <c r="M83" s="9" t="n"/>
+      <c r="N83" s="9" t="n"/>
     </row>
     <row r="84" ht="15" customHeight="1">
       <c r="A84" s="7" t="inlineStr">
@@ -3859,6 +4327,12 @@
       <c r="L84" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M84" s="9" t="n">
+        <v>48</v>
+      </c>
+      <c r="N84" s="9" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="85" ht="15" customHeight="1">
       <c r="A85" s="7" t="inlineStr">
@@ -3899,6 +4373,12 @@
       <c r="L85" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M85" s="9" t="n">
+        <v>2348</v>
+      </c>
+      <c r="N85" s="9" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="86" ht="15" customHeight="1">
       <c r="A86" s="7" t="inlineStr">
@@ -3939,6 +4419,12 @@
       <c r="L86" s="9" t="n">
         <v>10</v>
       </c>
+      <c r="M86" s="9" t="n">
+        <v>71</v>
+      </c>
+      <c r="N86" s="9" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="87" ht="15" customHeight="1">
       <c r="A87" s="7" t="inlineStr">
@@ -3979,6 +4465,12 @@
       <c r="L87" s="9" t="n">
         <v>26</v>
       </c>
+      <c r="M87" s="9" t="n">
+        <v>465</v>
+      </c>
+      <c r="N87" s="9" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="88" ht="15" customHeight="1">
       <c r="A88" s="7" t="inlineStr">
@@ -4019,6 +4511,12 @@
       <c r="L88" s="9" t="n">
         <v>18</v>
       </c>
+      <c r="M88" s="9" t="n">
+        <v>716</v>
+      </c>
+      <c r="N88" s="9" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="89" ht="15" customHeight="1">
       <c r="A89" s="7" t="inlineStr">
@@ -4059,6 +4557,12 @@
       <c r="L89" s="9" t="n">
         <v>79</v>
       </c>
+      <c r="M89" s="9" t="n">
+        <v>481</v>
+      </c>
+      <c r="N89" s="9" t="n">
+        <v>75</v>
+      </c>
     </row>
     <row r="90" ht="15" customHeight="1">
       <c r="A90" s="7" t="inlineStr">
@@ -4099,6 +4603,12 @@
       <c r="L90" s="9" t="n">
         <v>112</v>
       </c>
+      <c r="M90" s="9" t="n">
+        <v>6313</v>
+      </c>
+      <c r="N90" s="9" t="n">
+        <v>119</v>
+      </c>
     </row>
     <row r="91" ht="15" customHeight="1">
       <c r="A91" s="7" t="inlineStr">
@@ -4139,6 +4649,12 @@
       <c r="L91" s="9" t="n">
         <v>8</v>
       </c>
+      <c r="M91" s="9" t="n">
+        <v>70</v>
+      </c>
+      <c r="N91" s="9" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="92" ht="15" customHeight="1">
       <c r="A92" s="7" t="inlineStr">
@@ -4179,6 +4695,12 @@
       <c r="L92" s="9" t="n">
         <v>12</v>
       </c>
+      <c r="M92" s="9" t="n">
+        <v>4175</v>
+      </c>
+      <c r="N92" s="9" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="93" ht="15" customHeight="1">
       <c r="A93" s="7" t="inlineStr">
@@ -4219,6 +4741,12 @@
       <c r="L93" s="9" t="n">
         <v>9</v>
       </c>
+      <c r="M93" s="9" t="n">
+        <v>2949</v>
+      </c>
+      <c r="N93" s="9" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="94" ht="15" customHeight="1">
       <c r="A94" s="7" t="inlineStr">
@@ -4259,6 +4787,12 @@
       <c r="L94" s="9" t="n">
         <v>9</v>
       </c>
+      <c r="M94" s="9" t="n">
+        <v>1162</v>
+      </c>
+      <c r="N94" s="9" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="95" ht="15" customHeight="1">
       <c r="A95" s="7" t="inlineStr">
@@ -4299,6 +4833,12 @@
       <c r="L95" s="9" t="n">
         <v>18</v>
       </c>
+      <c r="M95" s="9" t="n">
+        <v>351</v>
+      </c>
+      <c r="N95" s="9" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="96" ht="15" customHeight="1">
       <c r="A96" s="7" t="inlineStr">
@@ -4337,6 +4877,12 @@
         <v>624</v>
       </c>
       <c r="L96" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="M96" s="9" t="n">
+        <v>646</v>
+      </c>
+      <c r="N96" s="9" t="n">
         <v>22</v>
       </c>
     </row>
@@ -4369,6 +4915,8 @@
       <c r="J97" s="9" t="n"/>
       <c r="K97" s="9" t="n"/>
       <c r="L97" s="9" t="n"/>
+      <c r="M97" s="9" t="n"/>
+      <c r="N97" s="9" t="n"/>
     </row>
     <row r="98" ht="15" customHeight="1">
       <c r="A98" s="7" t="inlineStr">
@@ -4409,6 +4957,12 @@
       <c r="L98" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M98" s="9" t="n">
+        <v>41</v>
+      </c>
+      <c r="N98" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="99" ht="15" customHeight="1">
       <c r="A99" s="7" t="inlineStr">
@@ -4449,6 +5003,12 @@
       <c r="L99" s="9" t="n">
         <v>20</v>
       </c>
+      <c r="M99" s="9" t="n">
+        <v>3271</v>
+      </c>
+      <c r="N99" s="9" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="100" ht="15" customHeight="1">
       <c r="A100" s="7" t="inlineStr">
@@ -4489,6 +5049,12 @@
       <c r="L100" s="9" t="n">
         <v>29</v>
       </c>
+      <c r="M100" s="9" t="n">
+        <v>1195</v>
+      </c>
+      <c r="N100" s="9" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="101" ht="15" customHeight="1">
       <c r="A101" s="7" t="inlineStr">
@@ -4529,6 +5095,12 @@
       <c r="L101" s="9" t="n">
         <v>16</v>
       </c>
+      <c r="M101" s="9" t="n">
+        <v>104</v>
+      </c>
+      <c r="N101" s="9" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="102" ht="15" customHeight="1">
       <c r="A102" s="7" t="inlineStr">
@@ -4569,6 +5141,12 @@
       <c r="L102" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M102" s="9" t="n">
+        <v>323</v>
+      </c>
+      <c r="N102" s="9" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="103" ht="15" customHeight="1">
       <c r="A103" s="7" t="inlineStr">
@@ -4608,6 +5186,12 @@
       </c>
       <c r="L103" s="9" t="n">
         <v>23</v>
+      </c>
+      <c r="M103" s="9" t="n">
+        <v>146</v>
+      </c>
+      <c r="N103" s="9" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="104" ht="15" customHeight="1">
@@ -4639,6 +5223,8 @@
       <c r="J104" s="9" t="n"/>
       <c r="K104" s="9" t="n"/>
       <c r="L104" s="9" t="n"/>
+      <c r="M104" s="9" t="n"/>
+      <c r="N104" s="9" t="n"/>
     </row>
     <row r="105" ht="15" customHeight="1">
       <c r="A105" s="7" t="inlineStr">
@@ -4679,6 +5265,12 @@
       <c r="L105" s="9" t="n">
         <v>11</v>
       </c>
+      <c r="M105" s="9" t="n">
+        <v>3052</v>
+      </c>
+      <c r="N105" s="9" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="106" ht="15" customHeight="1">
       <c r="A106" s="7" t="inlineStr">
@@ -4718,6 +5310,12 @@
       </c>
       <c r="L106" s="9" t="n">
         <v>12</v>
+      </c>
+      <c r="M106" s="9" t="n">
+        <v>270</v>
+      </c>
+      <c r="N106" s="9" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="107" ht="15" customHeight="1">
@@ -4749,6 +5347,8 @@
       <c r="J107" s="9" t="n"/>
       <c r="K107" s="9" t="n"/>
       <c r="L107" s="9" t="n"/>
+      <c r="M107" s="9" t="n"/>
+      <c r="N107" s="9" t="n"/>
     </row>
     <row r="108" ht="15" customHeight="1">
       <c r="A108" s="7" t="inlineStr">
@@ -4789,6 +5389,12 @@
       <c r="L108" s="9" t="n">
         <v>9</v>
       </c>
+      <c r="M108" s="9" t="n">
+        <v>1006</v>
+      </c>
+      <c r="N108" s="9" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="109" ht="15" customHeight="1">
       <c r="A109" s="7" t="inlineStr">
@@ -4829,6 +5435,12 @@
       <c r="L109" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M109" s="9" t="n">
+        <v>87</v>
+      </c>
+      <c r="N109" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="110" ht="15" customHeight="1">
       <c r="A110" s="7" t="inlineStr">
@@ -4869,6 +5481,12 @@
       <c r="L110" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M110" s="9" t="n">
+        <v>1026</v>
+      </c>
+      <c r="N110" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="111" ht="15" customHeight="1">
       <c r="A111" s="7" t="inlineStr">
@@ -4909,6 +5527,12 @@
       <c r="L111" s="9" t="n">
         <v>27</v>
       </c>
+      <c r="M111" s="9" t="n">
+        <v>113</v>
+      </c>
+      <c r="N111" s="9" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="112" ht="15" customHeight="1">
       <c r="A112" s="7" t="inlineStr">
@@ -4949,6 +5573,12 @@
       <c r="L112" s="9" t="n">
         <v>17</v>
       </c>
+      <c r="M112" s="9" t="n">
+        <v>1135</v>
+      </c>
+      <c r="N112" s="9" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="113" ht="15" customHeight="1">
       <c r="A113" s="7" t="inlineStr">
@@ -4989,6 +5619,12 @@
       <c r="L113" s="9" t="n">
         <v>27</v>
       </c>
+      <c r="M113" s="9" t="n">
+        <v>4389</v>
+      </c>
+      <c r="N113" s="9" t="n">
+        <v>31</v>
+      </c>
     </row>
     <row r="114" ht="15" customHeight="1">
       <c r="A114" s="7" t="inlineStr">
@@ -5029,6 +5665,12 @@
       <c r="L114" s="9" t="n">
         <v>18</v>
       </c>
+      <c r="M114" s="9" t="n">
+        <v>102</v>
+      </c>
+      <c r="N114" s="9" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="115" ht="15" customHeight="1">
       <c r="A115" s="7" t="inlineStr">
@@ -5069,6 +5711,12 @@
       <c r="L115" s="9" t="n">
         <v>12</v>
       </c>
+      <c r="M115" s="9" t="n">
+        <v>3160</v>
+      </c>
+      <c r="N115" s="9" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="116" ht="15" customHeight="1">
       <c r="A116" s="7" t="inlineStr">
@@ -5109,6 +5757,12 @@
       <c r="L116" s="9" t="n">
         <v>9</v>
       </c>
+      <c r="M116" s="9" t="n">
+        <v>123</v>
+      </c>
+      <c r="N116" s="9" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="117" ht="15" customHeight="1">
       <c r="A117" s="7" t="inlineStr">
@@ -5149,6 +5803,12 @@
       <c r="L117" s="9" t="n">
         <v>8</v>
       </c>
+      <c r="M117" s="9" t="n">
+        <v>379</v>
+      </c>
+      <c r="N117" s="9" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="118" ht="15" customHeight="1">
       <c r="A118" s="7" t="inlineStr">
@@ -5189,6 +5849,12 @@
       <c r="L118" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M118" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="N118" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="119" ht="15" customHeight="1">
       <c r="A119" s="7" t="inlineStr">
@@ -5228,6 +5894,12 @@
       </c>
       <c r="L119" s="9" t="n">
         <v>14</v>
+      </c>
+      <c r="M119" s="9" t="n">
+        <v>921</v>
+      </c>
+      <c r="N119" s="9" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="120" ht="15" customHeight="1">
@@ -5259,6 +5931,8 @@
       <c r="J120" s="9" t="n"/>
       <c r="K120" s="9" t="n"/>
       <c r="L120" s="9" t="n"/>
+      <c r="M120" s="9" t="n"/>
+      <c r="N120" s="9" t="n"/>
     </row>
     <row r="121" ht="15" customHeight="1">
       <c r="A121" s="7" t="inlineStr">
@@ -5299,6 +5973,12 @@
       <c r="L121" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M121" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="N121" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="122" ht="15" customHeight="1">
       <c r="A122" s="7" t="inlineStr">
@@ -5339,6 +6019,12 @@
       <c r="L122" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M122" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N122" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="123" ht="15" customHeight="1">
       <c r="A123" s="7" t="inlineStr">
@@ -5379,6 +6065,12 @@
       <c r="L123" s="9" t="n">
         <v>15</v>
       </c>
+      <c r="M123" s="9" t="n">
+        <v>804</v>
+      </c>
+      <c r="N123" s="9" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="124" ht="15" customHeight="1">
       <c r="A124" s="7" t="inlineStr">
@@ -5419,6 +6111,12 @@
       <c r="L124" s="9" t="n">
         <v>32</v>
       </c>
+      <c r="M124" s="9" t="n">
+        <v>2407</v>
+      </c>
+      <c r="N124" s="9" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="125" ht="15" customHeight="1">
       <c r="A125" s="7" t="inlineStr">
@@ -5459,6 +6157,12 @@
       <c r="L125" s="9" t="n">
         <v>9</v>
       </c>
+      <c r="M125" s="9" t="n">
+        <v>69</v>
+      </c>
+      <c r="N125" s="9" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="126" ht="15" customHeight="1">
       <c r="A126" s="7" t="inlineStr">
@@ -5499,6 +6203,12 @@
       <c r="L126" s="9" t="n">
         <v>73</v>
       </c>
+      <c r="M126" s="9" t="n">
+        <v>456</v>
+      </c>
+      <c r="N126" s="9" t="n">
+        <v>62</v>
+      </c>
     </row>
     <row r="127" ht="15" customHeight="1">
       <c r="A127" s="7" t="inlineStr">
@@ -5539,6 +6249,12 @@
       <c r="L127" s="9" t="n">
         <v>10</v>
       </c>
+      <c r="M127" s="9" t="n">
+        <v>66</v>
+      </c>
+      <c r="N127" s="9" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="128" ht="15" customHeight="1">
       <c r="A128" s="7" t="inlineStr">
@@ -5579,6 +6295,12 @@
       <c r="L128" s="9" t="n">
         <v>18</v>
       </c>
+      <c r="M128" s="9" t="n">
+        <v>154</v>
+      </c>
+      <c r="N128" s="9" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="129" ht="15" customHeight="1">
       <c r="A129" s="7" t="inlineStr">
@@ -5619,6 +6341,12 @@
       <c r="L129" s="9" t="n">
         <v>27</v>
       </c>
+      <c r="M129" s="9" t="n">
+        <v>382</v>
+      </c>
+      <c r="N129" s="9" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="130" ht="15" customHeight="1">
       <c r="A130" s="7" t="inlineStr">
@@ -5659,6 +6387,12 @@
       <c r="L130" s="9" t="n">
         <v>17</v>
       </c>
+      <c r="M130" s="9" t="n">
+        <v>305</v>
+      </c>
+      <c r="N130" s="9" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="131" ht="15" customHeight="1">
       <c r="A131" s="7" t="inlineStr">
@@ -5699,6 +6433,12 @@
       <c r="L131" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M131" s="9" t="n">
+        <v>17</v>
+      </c>
+      <c r="N131" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="132" ht="15" customHeight="1">
       <c r="A132" s="7" t="inlineStr">
@@ -5739,6 +6479,12 @@
       <c r="L132" s="9" t="n">
         <v>10</v>
       </c>
+      <c r="M132" s="9" t="n">
+        <v>781</v>
+      </c>
+      <c r="N132" s="9" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="133" ht="15" customHeight="1">
       <c r="A133" s="7" t="inlineStr">
@@ -5779,6 +6525,12 @@
       <c r="L133" s="9" t="n">
         <v>42</v>
       </c>
+      <c r="M133" s="9" t="n">
+        <v>132</v>
+      </c>
+      <c r="N133" s="9" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="134" ht="15" customHeight="1">
       <c r="A134" s="7" t="inlineStr">
@@ -5819,6 +6571,12 @@
       <c r="L134" s="9" t="n">
         <v>22</v>
       </c>
+      <c r="M134" s="9" t="n">
+        <v>954</v>
+      </c>
+      <c r="N134" s="9" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="135" ht="15" customHeight="1">
       <c r="A135" s="7" t="inlineStr">
@@ -5859,6 +6617,12 @@
       <c r="L135" s="9" t="n">
         <v>20</v>
       </c>
+      <c r="M135" s="9" t="n">
+        <v>157</v>
+      </c>
+      <c r="N135" s="9" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="136" ht="15" customHeight="1">
       <c r="A136" s="7" t="inlineStr">
@@ -5899,6 +6663,12 @@
       <c r="L136" s="9" t="n">
         <v>8</v>
       </c>
+      <c r="M136" s="9" t="n">
+        <v>56</v>
+      </c>
+      <c r="N136" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="137" ht="15" customHeight="1">
       <c r="A137" s="7" t="inlineStr">
@@ -5939,6 +6709,12 @@
       <c r="L137" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M137" s="9" t="n">
+        <v>53</v>
+      </c>
+      <c r="N137" s="9" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="138" ht="15" customHeight="1">
       <c r="A138" s="7" t="inlineStr">
@@ -5979,6 +6755,12 @@
       <c r="L138" s="9" t="n">
         <v>22</v>
       </c>
+      <c r="M138" s="9" t="n">
+        <v>581</v>
+      </c>
+      <c r="N138" s="9" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="139" ht="15" customHeight="1">
       <c r="A139" s="7" t="inlineStr">
@@ -6019,6 +6801,12 @@
       <c r="L139" s="9" t="n">
         <v>23</v>
       </c>
+      <c r="M139" s="9" t="n">
+        <v>169</v>
+      </c>
+      <c r="N139" s="9" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="140" ht="15" customHeight="1">
       <c r="A140" s="7" t="inlineStr">
@@ -6059,6 +6847,12 @@
       <c r="L140" s="9" t="n">
         <v>20</v>
       </c>
+      <c r="M140" s="9" t="n">
+        <v>1870</v>
+      </c>
+      <c r="N140" s="9" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="141" ht="15" customHeight="1">
       <c r="A141" s="7" t="inlineStr">
@@ -6099,6 +6893,12 @@
       <c r="L141" s="9" t="n">
         <v>21</v>
       </c>
+      <c r="M141" s="9" t="n">
+        <v>5377</v>
+      </c>
+      <c r="N141" s="9" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="142" ht="15" customHeight="1">
       <c r="A142" s="7" t="inlineStr">
@@ -6138,6 +6938,12 @@
       </c>
       <c r="L142" s="9" t="n">
         <v>16</v>
+      </c>
+      <c r="M142" s="9" t="n">
+        <v>1153</v>
+      </c>
+      <c r="N142" s="9" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="143" ht="15" customHeight="1">
@@ -6169,6 +6975,8 @@
       <c r="J143" s="9" t="n"/>
       <c r="K143" s="9" t="n"/>
       <c r="L143" s="9" t="n"/>
+      <c r="M143" s="9" t="n"/>
+      <c r="N143" s="9" t="n"/>
     </row>
     <row r="144" ht="15" customHeight="1">
       <c r="A144" s="7" t="inlineStr">
@@ -6209,6 +7017,12 @@
       <c r="L144" s="9" t="n">
         <v>10</v>
       </c>
+      <c r="M144" s="9" t="n">
+        <v>89</v>
+      </c>
+      <c r="N144" s="9" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="145" ht="15" customHeight="1">
       <c r="A145" s="7" t="inlineStr">
@@ -6249,6 +7063,12 @@
       <c r="L145" s="9" t="n">
         <v>28</v>
       </c>
+      <c r="M145" s="9" t="n">
+        <v>92</v>
+      </c>
+      <c r="N145" s="9" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="146" ht="15" customHeight="1">
       <c r="A146" s="7" t="inlineStr">
@@ -6289,6 +7109,12 @@
       <c r="L146" s="9" t="n">
         <v>34</v>
       </c>
+      <c r="M146" s="9" t="n">
+        <v>199</v>
+      </c>
+      <c r="N146" s="9" t="n">
+        <v>33</v>
+      </c>
     </row>
     <row r="147" ht="15" customHeight="1">
       <c r="A147" s="7" t="inlineStr">
@@ -6329,6 +7155,12 @@
       <c r="L147" s="9" t="n">
         <v>21</v>
       </c>
+      <c r="M147" s="9" t="n">
+        <v>120</v>
+      </c>
+      <c r="N147" s="9" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="148" ht="15" customHeight="1">
       <c r="A148" s="7" t="inlineStr">
@@ -6369,6 +7201,12 @@
       <c r="L148" s="9" t="n">
         <v>18</v>
       </c>
+      <c r="M148" s="9" t="n">
+        <v>2268</v>
+      </c>
+      <c r="N148" s="9" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="149" ht="15" customHeight="1">
       <c r="A149" s="7" t="inlineStr">
@@ -6409,6 +7247,12 @@
       <c r="L149" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M149" s="9" t="n">
+        <v>36</v>
+      </c>
+      <c r="N149" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="150" ht="15" customHeight="1">
       <c r="A150" s="7" t="inlineStr">
@@ -6448,6 +7292,12 @@
       </c>
       <c r="L150" s="9" t="n">
         <v>9</v>
+      </c>
+      <c r="M150" s="9" t="n">
+        <v>517</v>
+      </c>
+      <c r="N150" s="9" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="151" ht="15" customHeight="1">
@@ -6479,6 +7329,8 @@
       <c r="J151" s="9" t="n"/>
       <c r="K151" s="9" t="n"/>
       <c r="L151" s="9" t="n"/>
+      <c r="M151" s="9" t="n"/>
+      <c r="N151" s="9" t="n"/>
     </row>
     <row r="152" ht="15" customHeight="1">
       <c r="A152" s="7" t="inlineStr">
@@ -6508,10 +7360,16 @@
       <c r="I152" s="9" t="n"/>
       <c r="J152" s="9" t="n"/>
       <c r="K152" s="9" t="n">
-        <v>25</v>
+        <v>159</v>
       </c>
       <c r="L152" s="9" t="n">
         <v>15</v>
+      </c>
+      <c r="M152" s="9" t="n">
+        <v>168</v>
+      </c>
+      <c r="N152" s="9" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="153" ht="15" customHeight="1">
@@ -6549,6 +7407,8 @@
       </c>
       <c r="K153" s="9" t="n"/>
       <c r="L153" s="9" t="n"/>
+      <c r="M153" s="9" t="n"/>
+      <c r="N153" s="9" t="n"/>
     </row>
     <row r="154" ht="15" customHeight="1">
       <c r="A154" s="7" t="inlineStr">
@@ -6589,6 +7449,12 @@
       <c r="L154" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M154" s="9" t="n">
+        <v>41</v>
+      </c>
+      <c r="N154" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="155" ht="15" customHeight="1">
       <c r="A155" s="7" t="inlineStr">
@@ -6629,6 +7495,12 @@
       <c r="L155" s="9" t="n">
         <v>18</v>
       </c>
+      <c r="M155" s="9" t="n">
+        <v>127</v>
+      </c>
+      <c r="N155" s="9" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="156" ht="15" customHeight="1">
       <c r="A156" s="7" t="inlineStr">
@@ -6669,6 +7541,12 @@
       <c r="L156" s="9" t="n">
         <v>19</v>
       </c>
+      <c r="M156" s="9" t="n">
+        <v>131</v>
+      </c>
+      <c r="N156" s="9" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="157" ht="15" customHeight="1">
       <c r="A157" s="7" t="inlineStr">
@@ -6709,6 +7587,12 @@
       <c r="L157" s="9" t="n">
         <v>23</v>
       </c>
+      <c r="M157" s="9" t="n">
+        <v>1834</v>
+      </c>
+      <c r="N157" s="9" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="158" ht="15" customHeight="1">
       <c r="A158" s="7" t="inlineStr">
@@ -6749,6 +7633,12 @@
       <c r="L158" s="9" t="n">
         <v>14</v>
       </c>
+      <c r="M158" s="9" t="n">
+        <v>847</v>
+      </c>
+      <c r="N158" s="9" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="159" ht="15" customHeight="1">
       <c r="A159" s="7" t="inlineStr">
@@ -6789,6 +7679,12 @@
       <c r="L159" s="9" t="n">
         <v>16</v>
       </c>
+      <c r="M159" s="9" t="n">
+        <v>373</v>
+      </c>
+      <c r="N159" s="9" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="160" ht="15" customHeight="1">
       <c r="A160" s="7" t="inlineStr">
@@ -6829,6 +7725,12 @@
       <c r="L160" s="9" t="n">
         <v>7</v>
       </c>
+      <c r="M160" s="9" t="n">
+        <v>362</v>
+      </c>
+      <c r="N160" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="161" ht="15" customHeight="1">
       <c r="A161" s="7" t="inlineStr">
@@ -6869,6 +7771,12 @@
       <c r="L161" s="9" t="n">
         <v>18</v>
       </c>
+      <c r="M161" s="9" t="n">
+        <v>583</v>
+      </c>
+      <c r="N161" s="9" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="162" ht="15" customHeight="1">
       <c r="A162" s="7" t="inlineStr">
@@ -6909,6 +7817,12 @@
       <c r="L162" s="9" t="n">
         <v>26</v>
       </c>
+      <c r="M162" s="9" t="n">
+        <v>122</v>
+      </c>
+      <c r="N162" s="9" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="163" ht="15" customHeight="1">
       <c r="A163" s="7" t="inlineStr">
@@ -6949,6 +7863,12 @@
       <c r="L163" s="9" t="n">
         <v>18</v>
       </c>
+      <c r="M163" s="9" t="n">
+        <v>2317</v>
+      </c>
+      <c r="N163" s="9" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="164" ht="15" customHeight="1">
       <c r="A164" s="7" t="inlineStr">
@@ -6989,6 +7909,12 @@
       <c r="L164" s="9" t="n">
         <v>24</v>
       </c>
+      <c r="M164" s="9" t="n">
+        <v>3444</v>
+      </c>
+      <c r="N164" s="9" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="165" ht="15" customHeight="1">
       <c r="A165" s="7" t="inlineStr">
@@ -7029,6 +7955,12 @@
       <c r="L165" s="9" t="n">
         <v>10</v>
       </c>
+      <c r="M165" s="9" t="n">
+        <v>2510</v>
+      </c>
+      <c r="N165" s="9" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="166" ht="15" customHeight="1">
       <c r="A166" s="7" t="inlineStr">
@@ -7068,6 +8000,12 @@
       </c>
       <c r="L166" s="9" t="n">
         <v>18</v>
+      </c>
+      <c r="M166" s="9" t="n">
+        <v>74</v>
+      </c>
+      <c r="N166" s="9" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="167" ht="15" customHeight="1">
@@ -7099,6 +8037,8 @@
       <c r="J167" s="9" t="n"/>
       <c r="K167" s="9" t="n"/>
       <c r="L167" s="9" t="n"/>
+      <c r="M167" s="9" t="n"/>
+      <c r="N167" s="9" t="n"/>
     </row>
     <row r="168" ht="15" customHeight="1">
       <c r="A168" s="7" t="inlineStr">
@@ -7139,6 +8079,12 @@
       <c r="L168" s="9" t="n">
         <v>33</v>
       </c>
+      <c r="M168" s="9" t="n">
+        <v>236</v>
+      </c>
+      <c r="N168" s="9" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="169" ht="15" customHeight="1">
       <c r="A169" s="7" t="inlineStr">
@@ -7179,6 +8125,12 @@
       <c r="L169" s="9" t="n">
         <v>15</v>
       </c>
+      <c r="M169" s="9" t="n">
+        <v>103</v>
+      </c>
+      <c r="N169" s="9" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="170" ht="15" customHeight="1">
       <c r="A170" s="7" t="inlineStr">
@@ -7219,6 +8171,12 @@
       <c r="L170" s="9" t="n">
         <v>15</v>
       </c>
+      <c r="M170" s="9" t="n">
+        <v>76</v>
+      </c>
+      <c r="N170" s="9" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="171" ht="15" customHeight="1">
       <c r="A171" s="7" t="inlineStr">
@@ -7259,6 +8217,12 @@
       <c r="L171" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M171" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="N171" s="9" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="172" ht="15" customHeight="1">
       <c r="A172" s="7" t="inlineStr">
@@ -7299,6 +8263,12 @@
       <c r="L172" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M172" s="9" t="n">
+        <v>29</v>
+      </c>
+      <c r="N172" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="173" ht="15" customHeight="1">
       <c r="A173" s="7" t="inlineStr">
@@ -7339,6 +8309,12 @@
       <c r="L173" s="9" t="n">
         <v>10</v>
       </c>
+      <c r="M173" s="9" t="n">
+        <v>75</v>
+      </c>
+      <c r="N173" s="9" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="174" ht="15" customHeight="1">
       <c r="A174" s="7" t="inlineStr">
@@ -7379,6 +8355,12 @@
       <c r="L174" s="9" t="n">
         <v>25</v>
       </c>
+      <c r="M174" s="9" t="n">
+        <v>427</v>
+      </c>
+      <c r="N174" s="9" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="175" ht="15" customHeight="1">
       <c r="A175" s="7" t="inlineStr">
@@ -7419,6 +8401,12 @@
       <c r="L175" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M175" s="9" t="n">
+        <v>55</v>
+      </c>
+      <c r="N175" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="176" ht="15" customHeight="1">
       <c r="A176" s="7" t="inlineStr">
@@ -7459,6 +8447,12 @@
       <c r="L176" s="9" t="n">
         <v>8</v>
       </c>
+      <c r="M176" s="9" t="n">
+        <v>1235</v>
+      </c>
+      <c r="N176" s="9" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="177" ht="15" customHeight="1">
       <c r="A177" s="7" t="inlineStr">
@@ -7499,6 +8493,12 @@
       <c r="L177" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M177" s="9" t="n">
+        <v>42</v>
+      </c>
+      <c r="N177" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="178" ht="15" customHeight="1">
       <c r="A178" s="7" t="inlineStr">
@@ -7539,6 +8539,12 @@
       <c r="L178" s="9" t="n">
         <v>17</v>
       </c>
+      <c r="M178" s="9" t="n">
+        <v>120</v>
+      </c>
+      <c r="N178" s="9" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="179" ht="15" customHeight="1">
       <c r="A179" s="7" t="inlineStr">
@@ -7579,6 +8585,12 @@
       <c r="L179" s="9" t="n">
         <v>7</v>
       </c>
+      <c r="M179" s="9" t="n">
+        <v>55</v>
+      </c>
+      <c r="N179" s="9" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="180" ht="15" customHeight="1">
       <c r="A180" s="7" t="inlineStr">
@@ -7619,6 +8631,12 @@
       <c r="L180" s="9" t="n">
         <v>15</v>
       </c>
+      <c r="M180" s="9" t="n">
+        <v>57</v>
+      </c>
+      <c r="N180" s="9" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="181" ht="15" customHeight="1">
       <c r="A181" s="7" t="inlineStr">
@@ -7659,6 +8677,12 @@
       <c r="L181" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M181" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N181" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="182" ht="15" customHeight="1">
       <c r="A182" s="7" t="inlineStr">
@@ -7699,6 +8723,12 @@
       <c r="L182" s="9" t="n">
         <v>11</v>
       </c>
+      <c r="M182" s="9" t="n">
+        <v>92</v>
+      </c>
+      <c r="N182" s="9" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="183" ht="15" customHeight="1">
       <c r="A183" s="7" t="inlineStr">
@@ -7739,6 +8769,12 @@
       <c r="L183" s="9" t="n">
         <v>13</v>
       </c>
+      <c r="M183" s="9" t="n">
+        <v>2608</v>
+      </c>
+      <c r="N183" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="184" ht="15" customHeight="1">
       <c r="A184" s="7" t="inlineStr">
@@ -7779,6 +8815,12 @@
       <c r="L184" s="9" t="n">
         <v>17</v>
       </c>
+      <c r="M184" s="9" t="n">
+        <v>137</v>
+      </c>
+      <c r="N184" s="9" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="185" ht="15" customHeight="1">
       <c r="A185" s="7" t="inlineStr">
@@ -7819,6 +8861,12 @@
       <c r="L185" s="9" t="n">
         <v>10</v>
       </c>
+      <c r="M185" s="9" t="n">
+        <v>610</v>
+      </c>
+      <c r="N185" s="9" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="186" ht="15" customHeight="1">
       <c r="A186" s="7" t="inlineStr">
@@ -7859,6 +8907,12 @@
       <c r="L186" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M186" s="9" t="n">
+        <v>124</v>
+      </c>
+      <c r="N186" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="187" ht="15" customHeight="1">
       <c r="A187" s="7" t="inlineStr">
@@ -7899,6 +8953,12 @@
       <c r="L187" s="9" t="n">
         <v>8</v>
       </c>
+      <c r="M187" s="9" t="n">
+        <v>33</v>
+      </c>
+      <c r="N187" s="9" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="188" ht="15" customHeight="1">
       <c r="A188" s="7" t="inlineStr">
@@ -7939,6 +8999,12 @@
       <c r="L188" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M188" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="N188" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="189" ht="15" customHeight="1">
       <c r="A189" s="7" t="inlineStr">
@@ -7979,6 +9045,12 @@
       <c r="L189" s="9" t="n">
         <v>25</v>
       </c>
+      <c r="M189" s="9" t="n">
+        <v>56</v>
+      </c>
+      <c r="N189" s="9" t="n">
+        <v>31</v>
+      </c>
     </row>
     <row r="190" ht="15" customHeight="1">
       <c r="A190" s="7" t="inlineStr">
@@ -8019,6 +9091,12 @@
       <c r="L190" s="9" t="n">
         <v>15</v>
       </c>
+      <c r="M190" s="9" t="n">
+        <v>543</v>
+      </c>
+      <c r="N190" s="9" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="191" ht="15" customHeight="1">
       <c r="A191" s="7" t="inlineStr">
@@ -8059,6 +9137,12 @@
       <c r="L191" s="9" t="n">
         <v>17</v>
       </c>
+      <c r="M191" s="9" t="n">
+        <v>655</v>
+      </c>
+      <c r="N191" s="9" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="192" ht="15" customHeight="1">
       <c r="A192" s="7" t="inlineStr">
@@ -8099,6 +9183,12 @@
       <c r="L192" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M192" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="N192" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="193" ht="15" customHeight="1">
       <c r="A193" s="7" t="inlineStr">
@@ -8139,6 +9229,12 @@
       <c r="L193" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M193" s="9" t="n">
+        <v>534</v>
+      </c>
+      <c r="N193" s="9" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="194" ht="15" customHeight="1">
       <c r="A194" s="7" t="inlineStr">
@@ -8179,6 +9275,12 @@
       <c r="L194" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M194" s="9" t="n">
+        <v>99</v>
+      </c>
+      <c r="N194" s="9" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="195" ht="15" customHeight="1">
       <c r="A195" s="7" t="inlineStr">
@@ -8219,6 +9321,12 @@
       <c r="L195" s="9" t="n">
         <v>10</v>
       </c>
+      <c r="M195" s="9" t="n">
+        <v>77</v>
+      </c>
+      <c r="N195" s="9" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="196" ht="15" customHeight="1">
       <c r="A196" s="7" t="inlineStr">
@@ -8259,6 +9367,12 @@
       <c r="L196" s="9" t="n">
         <v>8</v>
       </c>
+      <c r="M196" s="9" t="n">
+        <v>49</v>
+      </c>
+      <c r="N196" s="9" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="197" ht="15" customHeight="1">
       <c r="A197" s="7" t="inlineStr">
@@ -8299,6 +9413,12 @@
       <c r="L197" s="9" t="n">
         <v>18</v>
       </c>
+      <c r="M197" s="9" t="n">
+        <v>114</v>
+      </c>
+      <c r="N197" s="9" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="198" ht="15" customHeight="1">
       <c r="A198" s="7" t="inlineStr">
@@ -8339,6 +9459,12 @@
       <c r="L198" s="9" t="n">
         <v>7</v>
       </c>
+      <c r="M198" s="9" t="n">
+        <v>53</v>
+      </c>
+      <c r="N198" s="9" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="199" ht="15" customHeight="1">
       <c r="A199" s="7" t="inlineStr">
@@ -8379,6 +9505,12 @@
       <c r="L199" s="9" t="n">
         <v>12</v>
       </c>
+      <c r="M199" s="9" t="n">
+        <v>101</v>
+      </c>
+      <c r="N199" s="9" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="200" ht="15" customHeight="1">
       <c r="A200" s="7" t="inlineStr">
@@ -8419,6 +9551,12 @@
       <c r="L200" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M200" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="N200" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="201" ht="15" customHeight="1">
       <c r="A201" s="7" t="inlineStr">
@@ -8459,6 +9597,12 @@
       <c r="L201" s="9" t="n">
         <v>8</v>
       </c>
+      <c r="M201" s="9" t="n">
+        <v>74</v>
+      </c>
+      <c r="N201" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="202" ht="15" customHeight="1">
       <c r="A202" s="7" t="inlineStr">
@@ -8499,6 +9643,12 @@
       <c r="L202" s="9" t="n">
         <v>11</v>
       </c>
+      <c r="M202" s="9" t="n">
+        <v>631</v>
+      </c>
+      <c r="N202" s="9" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="203" ht="15" customHeight="1">
       <c r="A203" s="7" t="inlineStr">
@@ -8539,6 +9689,12 @@
       <c r="L203" s="9" t="n">
         <v>12</v>
       </c>
+      <c r="M203" s="9" t="n">
+        <v>131</v>
+      </c>
+      <c r="N203" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="204" ht="15" customHeight="1">
       <c r="A204" s="7" t="inlineStr">
@@ -8579,6 +9735,12 @@
       <c r="L204" s="9" t="n">
         <v>12</v>
       </c>
+      <c r="M204" s="9" t="n">
+        <v>569</v>
+      </c>
+      <c r="N204" s="9" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="205" ht="15" customHeight="1">
       <c r="A205" s="7" t="inlineStr">
@@ -8619,6 +9781,12 @@
       <c r="L205" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M205" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N205" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="206" ht="15" customHeight="1">
       <c r="A206" s="7" t="inlineStr">
@@ -8659,6 +9827,12 @@
       <c r="L206" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M206" s="9" t="n">
+        <v>41</v>
+      </c>
+      <c r="N206" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="207" ht="15" customHeight="1">
       <c r="A207" s="7" t="inlineStr">
@@ -8698,6 +9872,12 @@
       </c>
       <c r="L207" s="9" t="n">
         <v>15</v>
+      </c>
+      <c r="M207" s="9" t="n">
+        <v>122</v>
+      </c>
+      <c r="N207" s="9" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="208" ht="15" customHeight="1">
@@ -8728,9 +9908,15 @@
       <c r="I208" s="9" t="n"/>
       <c r="J208" s="9" t="n"/>
       <c r="K208" s="9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L208" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="M208" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N208" s="9" t="n">
         <v>5</v>
       </c>
     </row>
@@ -8773,6 +9959,12 @@
       <c r="L209" s="9" t="n">
         <v>9</v>
       </c>
+      <c r="M209" s="9" t="n">
+        <v>95</v>
+      </c>
+      <c r="N209" s="9" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="210" ht="15" customHeight="1">
       <c r="A210" s="7" t="inlineStr">
@@ -8813,6 +10005,12 @@
       <c r="L210" s="9" t="n">
         <v>8</v>
       </c>
+      <c r="M210" s="9" t="n">
+        <v>79</v>
+      </c>
+      <c r="N210" s="9" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="211" ht="15" customHeight="1">
       <c r="A211" s="7" t="inlineStr">
@@ -8853,6 +10051,12 @@
       <c r="L211" s="9" t="n">
         <v>10</v>
       </c>
+      <c r="M211" s="9" t="n">
+        <v>84</v>
+      </c>
+      <c r="N211" s="9" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="212" ht="15" customHeight="1">
       <c r="A212" s="7" t="inlineStr">
@@ -8893,6 +10097,12 @@
       <c r="L212" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M212" s="9" t="n">
+        <v>183</v>
+      </c>
+      <c r="N212" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="213" ht="15" customHeight="1">
       <c r="A213" s="7" t="inlineStr">
@@ -8931,6 +10141,12 @@
         <v>700</v>
       </c>
       <c r="L213" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="M213" s="9" t="n">
+        <v>704</v>
+      </c>
+      <c r="N213" s="9" t="n">
         <v>5</v>
       </c>
     </row>
@@ -8963,6 +10179,8 @@
       <c r="J214" s="9" t="n"/>
       <c r="K214" s="9" t="n"/>
       <c r="L214" s="9" t="n"/>
+      <c r="M214" s="9" t="n"/>
+      <c r="N214" s="9" t="n"/>
     </row>
     <row r="215" ht="15" customHeight="1">
       <c r="A215" s="7" t="inlineStr">
@@ -9003,6 +10221,12 @@
       <c r="L215" s="9" t="n">
         <v>11</v>
       </c>
+      <c r="M215" s="9" t="n">
+        <v>1522</v>
+      </c>
+      <c r="N215" s="9" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="216" ht="15" customHeight="1">
       <c r="A216" s="7" t="inlineStr">
@@ -9038,10 +10262,16 @@
         <v>131</v>
       </c>
       <c r="K216" s="9" t="n">
-        <v>14357</v>
+        <v>14180</v>
       </c>
       <c r="L216" s="9" t="n">
         <v>295</v>
+      </c>
+      <c r="M216" s="9" t="n">
+        <v>14269</v>
+      </c>
+      <c r="N216" s="9" t="n">
+        <v>89</v>
       </c>
     </row>
     <row r="217" ht="15" customHeight="1">
@@ -9083,6 +10313,12 @@
       <c r="L217" s="9" t="n">
         <v>13</v>
       </c>
+      <c r="M217" s="9" t="n">
+        <v>78</v>
+      </c>
+      <c r="N217" s="9" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="218" ht="15" customHeight="1">
       <c r="A218" s="7" t="inlineStr">
@@ -9123,6 +10359,12 @@
       <c r="L218" s="9" t="n">
         <v>11</v>
       </c>
+      <c r="M218" s="9" t="n">
+        <v>67</v>
+      </c>
+      <c r="N218" s="9" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="219" ht="15" customHeight="1">
       <c r="A219" s="7" t="inlineStr">
@@ -9163,6 +10405,12 @@
       <c r="L219" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M219" s="9" t="n">
+        <v>132</v>
+      </c>
+      <c r="N219" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="220" ht="15" customHeight="1">
       <c r="A220" s="7" t="inlineStr">
@@ -9202,6 +10450,12 @@
       </c>
       <c r="L220" s="9" t="n">
         <v>23</v>
+      </c>
+      <c r="M220" s="9" t="n">
+        <v>156</v>
+      </c>
+      <c r="N220" s="9" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="221" ht="15" customHeight="1">
@@ -9233,6 +10487,8 @@
       <c r="J221" s="9" t="n"/>
       <c r="K221" s="9" t="n"/>
       <c r="L221" s="9" t="n"/>
+      <c r="M221" s="9" t="n"/>
+      <c r="N221" s="9" t="n"/>
     </row>
     <row r="222" ht="15" customHeight="1">
       <c r="A222" s="7" t="inlineStr">
@@ -9273,6 +10529,12 @@
       <c r="L222" s="9" t="n">
         <v>39</v>
       </c>
+      <c r="M222" s="9" t="n">
+        <v>266</v>
+      </c>
+      <c r="N222" s="9" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="223" ht="15" customHeight="1">
       <c r="A223" s="7" t="inlineStr">
@@ -9313,6 +10575,12 @@
       <c r="L223" s="9" t="n">
         <v>9</v>
       </c>
+      <c r="M223" s="9" t="n">
+        <v>300</v>
+      </c>
+      <c r="N223" s="9" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="224" ht="15" customHeight="1">
       <c r="A224" s="7" t="inlineStr">
@@ -9353,6 +10621,12 @@
       <c r="L224" s="9" t="n">
         <v>12</v>
       </c>
+      <c r="M224" s="9" t="n">
+        <v>36</v>
+      </c>
+      <c r="N224" s="9" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="225" ht="15" customHeight="1">
       <c r="A225" s="7" t="inlineStr">
@@ -9393,6 +10667,12 @@
       <c r="L225" s="9" t="n">
         <v>9</v>
       </c>
+      <c r="M225" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="N225" s="9" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="226" ht="15" customHeight="1">
       <c r="A226" s="7" t="inlineStr">
@@ -9433,6 +10713,12 @@
       <c r="L226" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M226" s="9" t="n">
+        <v>113</v>
+      </c>
+      <c r="N226" s="9" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="227" ht="15" customHeight="1">
       <c r="A227" s="7" t="inlineStr">
@@ -9473,6 +10759,12 @@
       <c r="L227" s="9" t="n">
         <v>11</v>
       </c>
+      <c r="M227" s="9" t="n">
+        <v>1121</v>
+      </c>
+      <c r="N227" s="9" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="228" ht="15" customHeight="1">
       <c r="A228" s="7" t="inlineStr">
@@ -9513,6 +10805,12 @@
       <c r="L228" s="9" t="n">
         <v>27</v>
       </c>
+      <c r="M228" s="9" t="n">
+        <v>1101</v>
+      </c>
+      <c r="N228" s="9" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="229" ht="15" customHeight="1">
       <c r="A229" s="7" t="inlineStr">
@@ -9553,6 +10851,12 @@
       <c r="L229" s="9" t="n">
         <v>7</v>
       </c>
+      <c r="M229" s="9" t="n">
+        <v>1347</v>
+      </c>
+      <c r="N229" s="9" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="230" ht="15" customHeight="1">
       <c r="A230" s="7" t="inlineStr">
@@ -9593,6 +10897,12 @@
       <c r="L230" s="9" t="n">
         <v>7</v>
       </c>
+      <c r="M230" s="9" t="n">
+        <v>351</v>
+      </c>
+      <c r="N230" s="9" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="231" ht="15" customHeight="1">
       <c r="A231" s="7" t="inlineStr">
@@ -9632,6 +10942,12 @@
       </c>
       <c r="L231" s="9" t="n">
         <v>15</v>
+      </c>
+      <c r="M231" s="9" t="n">
+        <v>603</v>
+      </c>
+      <c r="N231" s="9" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="232" ht="15" customHeight="1">
@@ -9663,6 +10979,8 @@
       <c r="J232" s="9" t="n"/>
       <c r="K232" s="9" t="n"/>
       <c r="L232" s="9" t="n"/>
+      <c r="M232" s="9" t="n"/>
+      <c r="N232" s="9" t="n"/>
     </row>
     <row r="233" ht="15" customHeight="1">
       <c r="A233" s="7" t="inlineStr">
@@ -9702,6 +11020,12 @@
       </c>
       <c r="L233" s="9" t="n">
         <v>12</v>
+      </c>
+      <c r="M233" s="9" t="n">
+        <v>92</v>
+      </c>
+      <c r="N233" s="9" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="234" ht="15" customHeight="1">
@@ -9733,6 +11057,8 @@
       <c r="J234" s="9" t="n"/>
       <c r="K234" s="9" t="n"/>
       <c r="L234" s="9" t="n"/>
+      <c r="M234" s="9" t="n"/>
+      <c r="N234" s="9" t="n"/>
     </row>
     <row r="235" ht="15" customHeight="1">
       <c r="A235" s="7" t="inlineStr">
@@ -9773,6 +11099,12 @@
       <c r="L235" s="9" t="n">
         <v>6</v>
       </c>
+      <c r="M235" s="9" t="n">
+        <v>49</v>
+      </c>
+      <c r="N235" s="9" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="236" ht="15" customHeight="1">
       <c r="A236" s="7" t="inlineStr">
@@ -9813,6 +11145,12 @@
       <c r="L236" s="9" t="n">
         <v>24</v>
       </c>
+      <c r="M236" s="9" t="n">
+        <v>146</v>
+      </c>
+      <c r="N236" s="9" t="n">
+        <v>27</v>
+      </c>
     </row>
     <row r="237" ht="15" customHeight="1">
       <c r="A237" s="7" t="inlineStr">
@@ -9853,6 +11191,12 @@
       <c r="L237" s="9" t="n">
         <v>17</v>
       </c>
+      <c r="M237" s="9" t="n">
+        <v>135</v>
+      </c>
+      <c r="N237" s="9" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="238" ht="15" customHeight="1">
       <c r="A238" s="7" t="inlineStr">
@@ -9893,6 +11237,12 @@
       <c r="L238" s="9" t="n">
         <v>10</v>
       </c>
+      <c r="M238" s="9" t="n">
+        <v>60</v>
+      </c>
+      <c r="N238" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="239" ht="15" customHeight="1">
       <c r="A239" s="7" t="inlineStr">
@@ -9933,6 +11283,12 @@
       <c r="L239" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M239" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="N239" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="240" ht="15" customHeight="1">
       <c r="A240" s="7" t="inlineStr">
@@ -9973,6 +11329,12 @@
       <c r="L240" s="9" t="n">
         <v>14</v>
       </c>
+      <c r="M240" s="9" t="n">
+        <v>90</v>
+      </c>
+      <c r="N240" s="9" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="241" ht="15" customHeight="1">
       <c r="A241" s="7" t="inlineStr">
@@ -10013,6 +11375,12 @@
       <c r="L241" s="9" t="n">
         <v>8</v>
       </c>
+      <c r="M241" s="9" t="n">
+        <v>85</v>
+      </c>
+      <c r="N241" s="9" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="242" ht="15" customHeight="1">
       <c r="A242" s="7" t="inlineStr">
@@ -10052,6 +11420,12 @@
       </c>
       <c r="L242" s="9" t="n">
         <v>21</v>
+      </c>
+      <c r="M242" s="9" t="n">
+        <v>145</v>
+      </c>
+      <c r="N242" s="9" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="243" ht="15" customHeight="1">
@@ -10074,15 +11448,29 @@
       <c r="E243" s="9" t="n"/>
       <c r="F243" s="9" t="n"/>
       <c r="G243" s="9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H243" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="I243" s="9" t="n"/>
-      <c r="J243" s="9" t="n"/>
-      <c r="K243" s="9" t="n"/>
-      <c r="L243" s="9" t="n"/>
+      <c r="I243" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J243" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="K243" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L243" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="M243" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="N243" s="9" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="244" ht="15" customHeight="1">
       <c r="A244" s="7" t="inlineStr">
@@ -10123,6 +11511,12 @@
       <c r="L244" s="9" t="n">
         <v>18</v>
       </c>
+      <c r="M244" s="9" t="n">
+        <v>115</v>
+      </c>
+      <c r="N244" s="9" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="245" ht="15" customHeight="1">
       <c r="A245" s="7" t="inlineStr">
@@ -10163,6 +11557,12 @@
       <c r="L245" s="9" t="n">
         <v>8</v>
       </c>
+      <c r="M245" s="9" t="n">
+        <v>51</v>
+      </c>
+      <c r="N245" s="9" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="246" ht="15" customHeight="1">
       <c r="A246" s="7" t="inlineStr">
@@ -10203,6 +11603,12 @@
       <c r="L246" s="9" t="n">
         <v>12</v>
       </c>
+      <c r="M246" s="9" t="n">
+        <v>75</v>
+      </c>
+      <c r="N246" s="9" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="247" ht="15" customHeight="1">
       <c r="A247" s="7" t="inlineStr">
@@ -10243,6 +11649,12 @@
       <c r="L247" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M247" s="9" t="n">
+        <v>1464</v>
+      </c>
+      <c r="N247" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="248" ht="15" customHeight="1">
       <c r="A248" s="7" t="inlineStr">
@@ -10283,6 +11695,12 @@
       <c r="L248" s="9" t="n">
         <v>18</v>
       </c>
+      <c r="M248" s="9" t="n">
+        <v>117</v>
+      </c>
+      <c r="N248" s="9" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="249" ht="15" customHeight="1">
       <c r="A249" s="7" t="inlineStr">
@@ -10321,6 +11739,12 @@
         <v>2467</v>
       </c>
       <c r="L249" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="M249" s="9" t="n">
+        <v>2475</v>
+      </c>
+      <c r="N249" s="9" t="n">
         <v>8</v>
       </c>
     </row>
@@ -10353,6 +11777,8 @@
       <c r="J250" s="9" t="n"/>
       <c r="K250" s="9" t="n"/>
       <c r="L250" s="9" t="n"/>
+      <c r="M250" s="9" t="n"/>
+      <c r="N250" s="9" t="n"/>
     </row>
     <row r="251" ht="15" customHeight="1">
       <c r="A251" s="7" t="inlineStr">
@@ -10393,6 +11819,12 @@
       <c r="L251" s="9" t="n">
         <v>21</v>
       </c>
+      <c r="M251" s="9" t="n">
+        <v>3316</v>
+      </c>
+      <c r="N251" s="9" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="252" ht="15" customHeight="1">
       <c r="A252" s="7" t="inlineStr">
@@ -10433,6 +11865,12 @@
       <c r="L252" s="9" t="n">
         <v>10</v>
       </c>
+      <c r="M252" s="9" t="n">
+        <v>3184</v>
+      </c>
+      <c r="N252" s="9" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="253" ht="15" customHeight="1">
       <c r="A253" s="7" t="inlineStr">
@@ -10473,6 +11911,12 @@
       <c r="L253" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M253" s="9" t="n">
+        <v>1192</v>
+      </c>
+      <c r="N253" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="254" ht="15" customHeight="1">
       <c r="A254" s="7" t="inlineStr">
@@ -10513,6 +11957,12 @@
       <c r="L254" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M254" s="9" t="n">
+        <v>47</v>
+      </c>
+      <c r="N254" s="9" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="255" ht="15" customHeight="1">
       <c r="A255" s="7" t="inlineStr">
@@ -10553,6 +12003,12 @@
       <c r="L255" s="9" t="n">
         <v>10</v>
       </c>
+      <c r="M255" s="9" t="n">
+        <v>323</v>
+      </c>
+      <c r="N255" s="9" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="256" ht="15" customHeight="1">
       <c r="A256" s="7" t="inlineStr">
@@ -10593,6 +12049,12 @@
       <c r="L256" s="9" t="n">
         <v>13</v>
       </c>
+      <c r="M256" s="9" t="n">
+        <v>4024</v>
+      </c>
+      <c r="N256" s="9" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="257" ht="15" customHeight="1">
       <c r="A257" s="7" t="inlineStr">
@@ -10633,6 +12095,12 @@
       <c r="L257" s="9" t="n">
         <v>14</v>
       </c>
+      <c r="M257" s="9" t="n">
+        <v>786</v>
+      </c>
+      <c r="N257" s="9" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="258" ht="15" customHeight="1">
       <c r="A258" s="7" t="inlineStr">
@@ -10673,6 +12141,12 @@
       <c r="L258" s="9" t="n">
         <v>10</v>
       </c>
+      <c r="M258" s="9" t="n">
+        <v>189</v>
+      </c>
+      <c r="N258" s="9" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="259" ht="15" customHeight="1">
       <c r="A259" s="7" t="inlineStr">
@@ -10713,6 +12187,12 @@
       <c r="L259" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M259" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N259" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="260" ht="15" customHeight="1">
       <c r="A260" s="7" t="inlineStr">
@@ -10753,6 +12233,12 @@
       <c r="L260" s="9" t="n">
         <v>9</v>
       </c>
+      <c r="M260" s="9" t="n">
+        <v>1184</v>
+      </c>
+      <c r="N260" s="9" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="261" ht="15" customHeight="1">
       <c r="A261" s="7" t="inlineStr">
@@ -10791,6 +12277,12 @@
         <v>10</v>
       </c>
       <c r="L261" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="M261" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="N261" s="9" t="n">
         <v>5</v>
       </c>
     </row>
@@ -10822,9 +12314,15 @@
       <c r="I262" s="9" t="n"/>
       <c r="J262" s="9" t="n"/>
       <c r="K262" s="9" t="n">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="L262" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="M262" s="9" t="n">
+        <v>38</v>
+      </c>
+      <c r="N262" s="9" t="n">
         <v>5</v>
       </c>
     </row>
@@ -10867,6 +12365,12 @@
       <c r="L263" s="9" t="n">
         <v>8</v>
       </c>
+      <c r="M263" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="N263" s="9" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="264" ht="15" customHeight="1">
       <c r="A264" s="7" t="inlineStr">
@@ -10907,6 +12411,12 @@
       <c r="L264" s="9" t="n">
         <v>6</v>
       </c>
+      <c r="M264" s="9" t="n">
+        <v>41</v>
+      </c>
+      <c r="N264" s="9" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="265" ht="15" customHeight="1">
       <c r="A265" s="7" t="inlineStr">
@@ -10947,6 +12457,12 @@
       <c r="L265" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M265" s="9" t="n">
+        <v>109</v>
+      </c>
+      <c r="N265" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="266" ht="15" customHeight="1">
       <c r="A266" s="7" t="inlineStr">
@@ -10987,6 +12503,12 @@
       <c r="L266" s="9" t="n">
         <v>6</v>
       </c>
+      <c r="M266" s="9" t="n">
+        <v>117</v>
+      </c>
+      <c r="N266" s="9" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="267" ht="15" customHeight="1">
       <c r="A267" s="7" t="inlineStr">
@@ -11027,6 +12549,12 @@
       <c r="L267" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M267" s="9" t="n">
+        <v>31</v>
+      </c>
+      <c r="N267" s="9" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="268" ht="15" customHeight="1">
       <c r="A268" s="7" t="inlineStr">
@@ -11067,6 +12595,12 @@
       <c r="L268" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M268" s="9" t="n">
+        <v>26</v>
+      </c>
+      <c r="N268" s="9" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="269" ht="15" customHeight="1">
       <c r="A269" s="7" t="inlineStr">
@@ -11107,6 +12641,12 @@
       <c r="L269" s="9" t="n">
         <v>15</v>
       </c>
+      <c r="M269" s="9" t="n">
+        <v>118</v>
+      </c>
+      <c r="N269" s="9" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="270" ht="15" customHeight="1">
       <c r="A270" s="7" t="inlineStr">
@@ -11147,6 +12687,12 @@
       <c r="L270" s="9" t="n">
         <v>23</v>
       </c>
+      <c r="M270" s="9" t="n">
+        <v>143</v>
+      </c>
+      <c r="N270" s="9" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="271" ht="15" customHeight="1">
       <c r="A271" s="7" t="inlineStr">
@@ -11187,6 +12733,12 @@
       <c r="L271" s="9" t="n">
         <v>15</v>
       </c>
+      <c r="M271" s="9" t="n">
+        <v>139</v>
+      </c>
+      <c r="N271" s="9" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="272" ht="15" customHeight="1">
       <c r="A272" s="7" t="inlineStr">
@@ -11227,6 +12779,12 @@
       <c r="L272" s="9" t="n">
         <v>16</v>
       </c>
+      <c r="M272" s="9" t="n">
+        <v>137</v>
+      </c>
+      <c r="N272" s="9" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="273" ht="15" customHeight="1">
       <c r="A273" s="7" t="inlineStr">
@@ -11267,6 +12825,12 @@
       <c r="L273" s="9" t="n">
         <v>17</v>
       </c>
+      <c r="M273" s="9" t="n">
+        <v>123</v>
+      </c>
+      <c r="N273" s="9" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="274" ht="15" customHeight="1">
       <c r="A274" s="7" t="inlineStr">
@@ -11307,6 +12871,12 @@
       <c r="L274" s="9" t="n">
         <v>16</v>
       </c>
+      <c r="M274" s="9" t="n">
+        <v>130</v>
+      </c>
+      <c r="N274" s="9" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="275" ht="15" customHeight="1">
       <c r="A275" s="7" t="inlineStr">
@@ -11347,6 +12917,12 @@
       <c r="L275" s="9" t="n">
         <v>6</v>
       </c>
+      <c r="M275" s="9" t="n">
+        <v>46</v>
+      </c>
+      <c r="N275" s="9" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="276" ht="15" customHeight="1">
       <c r="A276" s="7" t="inlineStr">
@@ -11385,6 +12961,12 @@
         <v>180</v>
       </c>
       <c r="L276" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="M276" s="9" t="n">
+        <v>183</v>
+      </c>
+      <c r="N276" s="9" t="n">
         <v>5</v>
       </c>
     </row>
@@ -11417,6 +12999,8 @@
       <c r="J277" s="9" t="n"/>
       <c r="K277" s="9" t="n"/>
       <c r="L277" s="9" t="n"/>
+      <c r="M277" s="9" t="n"/>
+      <c r="N277" s="9" t="n"/>
     </row>
     <row r="278" ht="15" customHeight="1">
       <c r="A278" s="7" t="inlineStr">
@@ -11457,6 +13041,12 @@
       <c r="L278" s="9" t="n">
         <v>19</v>
       </c>
+      <c r="M278" s="9" t="n">
+        <v>897</v>
+      </c>
+      <c r="N278" s="9" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="279" ht="15" customHeight="1">
       <c r="A279" s="7" t="inlineStr">
@@ -11497,6 +13087,12 @@
       <c r="L279" s="9" t="n">
         <v>8</v>
       </c>
+      <c r="M279" s="9" t="n">
+        <v>55</v>
+      </c>
+      <c r="N279" s="9" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="280" ht="15" customHeight="1">
       <c r="A280" s="7" t="inlineStr">
@@ -11537,6 +13133,12 @@
       <c r="L280" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M280" s="9" t="n">
+        <v>71</v>
+      </c>
+      <c r="N280" s="9" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="281" ht="15" customHeight="1">
       <c r="A281" s="7" t="inlineStr">
@@ -11577,6 +13179,12 @@
       <c r="L281" s="9" t="n">
         <v>7</v>
       </c>
+      <c r="M281" s="9" t="n">
+        <v>51</v>
+      </c>
+      <c r="N281" s="9" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="282" ht="15" customHeight="1">
       <c r="A282" s="7" t="inlineStr">
@@ -11617,6 +13225,12 @@
       <c r="L282" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M282" s="9" t="n">
+        <v>17</v>
+      </c>
+      <c r="N282" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="283" ht="15" customHeight="1">
       <c r="A283" s="7" t="inlineStr">
@@ -11657,6 +13271,12 @@
       <c r="L283" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M283" s="9" t="n">
+        <v>687</v>
+      </c>
+      <c r="N283" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="284" ht="15" customHeight="1">
       <c r="A284" s="7" t="inlineStr">
@@ -11697,6 +13317,12 @@
       <c r="L284" s="9" t="n">
         <v>6</v>
       </c>
+      <c r="M284" s="9" t="n">
+        <v>45</v>
+      </c>
+      <c r="N284" s="9" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="285" ht="15" customHeight="1">
       <c r="A285" s="7" t="inlineStr">
@@ -11737,6 +13363,12 @@
       <c r="L285" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M285" s="9" t="n">
+        <v>261</v>
+      </c>
+      <c r="N285" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="286" ht="15" customHeight="1">
       <c r="A286" s="7" t="inlineStr">
@@ -11777,6 +13409,12 @@
       <c r="L286" s="9" t="n">
         <v>11</v>
       </c>
+      <c r="M286" s="9" t="n">
+        <v>70</v>
+      </c>
+      <c r="N286" s="9" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="287" ht="15" customHeight="1">
       <c r="A287" s="7" t="inlineStr">
@@ -11817,6 +13455,12 @@
       <c r="L287" s="9" t="n">
         <v>15</v>
       </c>
+      <c r="M287" s="9" t="n">
+        <v>112</v>
+      </c>
+      <c r="N287" s="9" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="288" ht="15" customHeight="1">
       <c r="A288" s="7" t="inlineStr">
@@ -11857,6 +13501,12 @@
       <c r="L288" s="9" t="n">
         <v>9</v>
       </c>
+      <c r="M288" s="9" t="n">
+        <v>1355</v>
+      </c>
+      <c r="N288" s="9" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="289" ht="15" customHeight="1">
       <c r="A289" s="7" t="inlineStr">
@@ -11897,6 +13547,12 @@
       <c r="L289" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M289" s="9" t="n">
+        <v>256</v>
+      </c>
+      <c r="N289" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="290" ht="15" customHeight="1">
       <c r="A290" s="7" t="inlineStr">
@@ -11937,6 +13593,12 @@
       <c r="L290" s="9" t="n">
         <v>7</v>
       </c>
+      <c r="M290" s="9" t="n">
+        <v>33</v>
+      </c>
+      <c r="N290" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="291" ht="15" customHeight="1">
       <c r="A291" s="7" t="inlineStr">
@@ -11977,6 +13639,12 @@
       <c r="L291" s="9" t="n">
         <v>16</v>
       </c>
+      <c r="M291" s="9" t="n">
+        <v>106</v>
+      </c>
+      <c r="N291" s="9" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="292" ht="15" customHeight="1">
       <c r="A292" s="7" t="inlineStr">
@@ -12017,6 +13685,12 @@
       <c r="L292" s="9" t="n">
         <v>6</v>
       </c>
+      <c r="M292" s="9" t="n">
+        <v>677</v>
+      </c>
+      <c r="N292" s="9" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="293" ht="15" customHeight="1">
       <c r="A293" s="7" t="inlineStr">
@@ -12057,6 +13731,12 @@
       <c r="L293" s="9" t="n">
         <v>20</v>
       </c>
+      <c r="M293" s="9" t="n">
+        <v>1109</v>
+      </c>
+      <c r="N293" s="9" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="294" ht="15" customHeight="1">
       <c r="A294" s="7" t="inlineStr">
@@ -12097,6 +13777,12 @@
       <c r="L294" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M294" s="9" t="n">
+        <v>43</v>
+      </c>
+      <c r="N294" s="9" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="295" ht="15" customHeight="1">
       <c r="A295" s="7" t="inlineStr">
@@ -12137,6 +13823,12 @@
       <c r="L295" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M295" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="N295" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="296" ht="15" customHeight="1">
       <c r="A296" s="7" t="inlineStr">
@@ -12177,6 +13869,12 @@
       <c r="L296" s="9" t="n">
         <v>9</v>
       </c>
+      <c r="M296" s="9" t="n">
+        <v>417</v>
+      </c>
+      <c r="N296" s="9" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="297" ht="15" customHeight="1">
       <c r="A297" s="7" t="inlineStr">
@@ -12217,6 +13915,12 @@
       <c r="L297" s="9" t="n">
         <v>6</v>
       </c>
+      <c r="M297" s="9" t="n">
+        <v>41</v>
+      </c>
+      <c r="N297" s="9" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="298" ht="15" customHeight="1">
       <c r="A298" s="7" t="inlineStr">
@@ -12257,6 +13961,12 @@
       <c r="L298" s="9" t="n">
         <v>11</v>
       </c>
+      <c r="M298" s="9" t="n">
+        <v>276</v>
+      </c>
+      <c r="N298" s="9" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="299" ht="15" customHeight="1">
       <c r="A299" s="7" t="inlineStr">
@@ -12297,6 +14007,12 @@
       <c r="L299" s="9" t="n">
         <v>13</v>
       </c>
+      <c r="M299" s="9" t="n">
+        <v>1236</v>
+      </c>
+      <c r="N299" s="9" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="300" ht="15" customHeight="1">
       <c r="A300" s="7" t="inlineStr">
@@ -12337,6 +14053,12 @@
       <c r="L300" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M300" s="9" t="n">
+        <v>82</v>
+      </c>
+      <c r="N300" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="301" ht="15" customHeight="1">
       <c r="A301" s="7" t="inlineStr">
@@ -12377,6 +14099,12 @@
       <c r="L301" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M301" s="9" t="n">
+        <v>102</v>
+      </c>
+      <c r="N301" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="302" ht="15" customHeight="1">
       <c r="A302" s="7" t="inlineStr">
@@ -12417,6 +14145,12 @@
       <c r="L302" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M302" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="N302" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="303" ht="15" customHeight="1">
       <c r="A303" s="7" t="inlineStr">
@@ -12457,6 +14191,12 @@
       <c r="L303" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M303" s="9" t="n">
+        <v>45</v>
+      </c>
+      <c r="N303" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="304" ht="15" customHeight="1">
       <c r="A304" s="7" t="inlineStr">
@@ -12497,6 +14237,12 @@
       <c r="L304" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M304" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N304" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="305" ht="15" customHeight="1">
       <c r="A305" s="7" t="inlineStr">
@@ -12537,6 +14283,12 @@
       <c r="L305" s="9" t="n">
         <v>14</v>
       </c>
+      <c r="M305" s="9" t="n">
+        <v>1229</v>
+      </c>
+      <c r="N305" s="9" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="306" ht="15" customHeight="1">
       <c r="A306" s="7" t="inlineStr">
@@ -12577,6 +14329,12 @@
       <c r="L306" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M306" s="9" t="n">
+        <v>206</v>
+      </c>
+      <c r="N306" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="307" ht="15" customHeight="1">
       <c r="A307" s="7" t="inlineStr">
@@ -12617,6 +14375,12 @@
       <c r="L307" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M307" s="9" t="n">
+        <v>17</v>
+      </c>
+      <c r="N307" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="308" ht="15" customHeight="1">
       <c r="A308" s="7" t="inlineStr">
@@ -12657,6 +14421,12 @@
       <c r="L308" s="9" t="n">
         <v>12</v>
       </c>
+      <c r="M308" s="9" t="n">
+        <v>148</v>
+      </c>
+      <c r="N308" s="9" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="309" ht="15" customHeight="1">
       <c r="A309" s="7" t="inlineStr">
@@ -12697,6 +14467,12 @@
       <c r="L309" s="9" t="n">
         <v>12</v>
       </c>
+      <c r="M309" s="9" t="n">
+        <v>667</v>
+      </c>
+      <c r="N309" s="9" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="310" ht="15" customHeight="1">
       <c r="A310" s="7" t="inlineStr">
@@ -12737,6 +14513,12 @@
       <c r="L310" s="9" t="n">
         <v>22</v>
       </c>
+      <c r="M310" s="9" t="n">
+        <v>111</v>
+      </c>
+      <c r="N310" s="9" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="311" ht="15" customHeight="1">
       <c r="A311" s="7" t="inlineStr">
@@ -12777,6 +14559,12 @@
       <c r="L311" s="9" t="n">
         <v>39</v>
       </c>
+      <c r="M311" s="9" t="n">
+        <v>527</v>
+      </c>
+      <c r="N311" s="9" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="312" ht="15" customHeight="1">
       <c r="A312" s="7" t="inlineStr">
@@ -12816,6 +14604,12 @@
       </c>
       <c r="L312" s="9" t="n">
         <v>9</v>
+      </c>
+      <c r="M312" s="9" t="n">
+        <v>214</v>
+      </c>
+      <c r="N312" s="9" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="313" ht="15" customHeight="1">
@@ -12855,6 +14649,12 @@
       <c r="L313" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M313" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N313" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="314" ht="15" customHeight="1">
       <c r="A314" s="7" t="inlineStr">
@@ -12895,6 +14695,12 @@
       <c r="L314" s="9" t="n">
         <v>17</v>
       </c>
+      <c r="M314" s="9" t="n">
+        <v>1424</v>
+      </c>
+      <c r="N314" s="9" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="315" ht="15" customHeight="1">
       <c r="A315" s="7" t="inlineStr">
@@ -12934,6 +14740,12 @@
       </c>
       <c r="L315" s="9" t="n">
         <v>14</v>
+      </c>
+      <c r="M315" s="9" t="n">
+        <v>83</v>
+      </c>
+      <c r="N315" s="9" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="316" ht="15" customHeight="1">
@@ -12973,6 +14785,12 @@
       <c r="L316" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M316" s="9" t="n">
+        <v>23</v>
+      </c>
+      <c r="N316" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="317" ht="15" customHeight="1">
       <c r="A317" s="7" t="inlineStr">
@@ -13013,6 +14831,12 @@
       <c r="L317" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M317" s="9" t="n">
+        <v>759</v>
+      </c>
+      <c r="N317" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="318" ht="15" customHeight="1">
       <c r="A318" s="7" t="inlineStr">
@@ -13053,6 +14877,12 @@
       <c r="L318" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M318" s="9" t="n">
+        <v>38</v>
+      </c>
+      <c r="N318" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="319" ht="15" customHeight="1">
       <c r="A319" s="7" t="inlineStr">
@@ -13091,6 +14921,12 @@
         <v>305</v>
       </c>
       <c r="L319" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="M319" s="9" t="n">
+        <v>313</v>
+      </c>
+      <c r="N319" s="9" t="n">
         <v>8</v>
       </c>
     </row>
@@ -13123,6 +14959,8 @@
       <c r="J320" s="9" t="n"/>
       <c r="K320" s="9" t="n"/>
       <c r="L320" s="9" t="n"/>
+      <c r="M320" s="9" t="n"/>
+      <c r="N320" s="9" t="n"/>
     </row>
     <row r="321" ht="15" customHeight="1">
       <c r="A321" s="7" t="inlineStr">
@@ -13163,6 +15001,12 @@
       <c r="L321" s="9" t="n">
         <v>14</v>
       </c>
+      <c r="M321" s="9" t="n">
+        <v>105</v>
+      </c>
+      <c r="N321" s="9" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="322" ht="15" customHeight="1">
       <c r="A322" s="7" t="inlineStr">
@@ -13203,6 +15047,12 @@
       <c r="L322" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M322" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="N322" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="323" ht="15" customHeight="1">
       <c r="A323" s="7" t="inlineStr">
@@ -13243,6 +15093,12 @@
       <c r="L323" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M323" s="9" t="n">
+        <v>182</v>
+      </c>
+      <c r="N323" s="9" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="324" ht="15" customHeight="1">
       <c r="A324" s="7" t="inlineStr">
@@ -13282,6 +15138,12 @@
       </c>
       <c r="L324" s="9" t="n">
         <v>20</v>
+      </c>
+      <c r="M324" s="9" t="n">
+        <v>1384</v>
+      </c>
+      <c r="N324" s="9" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="325" ht="15" customHeight="1">
@@ -13313,6 +15175,8 @@
       <c r="J325" s="9" t="n"/>
       <c r="K325" s="9" t="n"/>
       <c r="L325" s="9" t="n"/>
+      <c r="M325" s="9" t="n"/>
+      <c r="N325" s="9" t="n"/>
     </row>
     <row r="326" ht="15" customHeight="1">
       <c r="A326" s="7" t="inlineStr">
@@ -13353,6 +15217,12 @@
       <c r="L326" s="9" t="n">
         <v>6</v>
       </c>
+      <c r="M326" s="9" t="n">
+        <v>144</v>
+      </c>
+      <c r="N326" s="9" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="327" ht="15" customHeight="1">
       <c r="A327" s="7" t="inlineStr">
@@ -13393,6 +15263,12 @@
       <c r="L327" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M327" s="9" t="n">
+        <v>118</v>
+      </c>
+      <c r="N327" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="328" ht="15" customHeight="1">
       <c r="A328" s="7" t="inlineStr">
@@ -13431,6 +15307,12 @@
         <v>60</v>
       </c>
       <c r="L328" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="M328" s="9" t="n">
+        <v>73</v>
+      </c>
+      <c r="N328" s="9" t="n">
         <v>13</v>
       </c>
     </row>
@@ -13463,6 +15345,8 @@
       <c r="J329" s="9" t="n"/>
       <c r="K329" s="9" t="n"/>
       <c r="L329" s="9" t="n"/>
+      <c r="M329" s="9" t="n"/>
+      <c r="N329" s="9" t="n"/>
     </row>
     <row r="330" ht="15" customHeight="1">
       <c r="A330" s="7" t="inlineStr">
@@ -13503,6 +15387,12 @@
       <c r="L330" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M330" s="9" t="n">
+        <v>363</v>
+      </c>
+      <c r="N330" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="331" ht="15" customHeight="1">
       <c r="A331" s="7" t="inlineStr">
@@ -13543,6 +15433,12 @@
       <c r="L331" s="9" t="n">
         <v>16</v>
       </c>
+      <c r="M331" s="9" t="n">
+        <v>900</v>
+      </c>
+      <c r="N331" s="9" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="332" ht="15" customHeight="1">
       <c r="A332" s="7" t="inlineStr">
@@ -13582,6 +15478,12 @@
       </c>
       <c r="L332" s="9" t="n">
         <v>6</v>
+      </c>
+      <c r="M332" s="9" t="n">
+        <v>2469</v>
+      </c>
+      <c r="N332" s="9" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="333" ht="15" customHeight="1">
@@ -13617,6 +15519,8 @@
       <c r="J333" s="9" t="n"/>
       <c r="K333" s="9" t="n"/>
       <c r="L333" s="9" t="n"/>
+      <c r="M333" s="9" t="n"/>
+      <c r="N333" s="9" t="n"/>
     </row>
     <row r="334" ht="15" customHeight="1">
       <c r="A334" s="7" t="inlineStr">
@@ -13657,6 +15561,12 @@
       <c r="L334" s="9" t="n">
         <v>13</v>
       </c>
+      <c r="M334" s="9" t="n">
+        <v>96</v>
+      </c>
+      <c r="N334" s="9" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="335" ht="15" customHeight="1">
       <c r="A335" s="7" t="inlineStr">
@@ -13697,6 +15607,12 @@
       <c r="L335" s="9" t="n">
         <v>31</v>
       </c>
+      <c r="M335" s="9" t="n">
+        <v>2193</v>
+      </c>
+      <c r="N335" s="9" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="336" ht="15" customHeight="1">
       <c r="A336" s="7" t="inlineStr">
@@ -13737,6 +15653,12 @@
       <c r="L336" s="9" t="n">
         <v>11</v>
       </c>
+      <c r="M336" s="9" t="n">
+        <v>1711</v>
+      </c>
+      <c r="N336" s="9" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="337" ht="15" customHeight="1">
       <c r="A337" s="7" t="inlineStr">
@@ -13777,6 +15699,12 @@
       <c r="L337" s="9" t="n">
         <v>18</v>
       </c>
+      <c r="M337" s="9" t="n">
+        <v>101</v>
+      </c>
+      <c r="N337" s="9" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="338" ht="15" customHeight="1">
       <c r="A338" s="7" t="inlineStr">
@@ -13816,6 +15744,12 @@
       </c>
       <c r="L338" s="9" t="n">
         <v>12</v>
+      </c>
+      <c r="M338" s="9" t="n">
+        <v>317</v>
+      </c>
+      <c r="N338" s="9" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="339" ht="15" customHeight="1">
@@ -13847,6 +15781,8 @@
       <c r="J339" s="9" t="n"/>
       <c r="K339" s="9" t="n"/>
       <c r="L339" s="9" t="n"/>
+      <c r="M339" s="9" t="n"/>
+      <c r="N339" s="9" t="n"/>
     </row>
     <row r="340" ht="15" customHeight="1">
       <c r="A340" s="7" t="inlineStr">
@@ -13887,6 +15823,12 @@
       <c r="L340" s="9" t="n">
         <v>12</v>
       </c>
+      <c r="M340" s="9" t="n">
+        <v>1108</v>
+      </c>
+      <c r="N340" s="9" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="341" ht="15" customHeight="1">
       <c r="A341" s="7" t="inlineStr">
@@ -13925,6 +15867,12 @@
         <v>879</v>
       </c>
       <c r="L341" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="M341" s="9" t="n">
+        <v>889</v>
+      </c>
+      <c r="N341" s="9" t="n">
         <v>10</v>
       </c>
     </row>
@@ -13955,8 +15903,18 @@
       </c>
       <c r="I342" s="9" t="n"/>
       <c r="J342" s="9" t="n"/>
-      <c r="K342" s="9" t="n"/>
-      <c r="L342" s="9" t="n"/>
+      <c r="K342" s="9" t="n">
+        <v>184</v>
+      </c>
+      <c r="L342" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="M342" s="9" t="n">
+        <v>193</v>
+      </c>
+      <c r="N342" s="9" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="343" ht="15" customHeight="1">
       <c r="A343" s="7" t="inlineStr">
@@ -13997,6 +15955,12 @@
       <c r="L343" s="9" t="n">
         <v>7</v>
       </c>
+      <c r="M343" s="9" t="n">
+        <v>1132</v>
+      </c>
+      <c r="N343" s="9" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="344" ht="15" customHeight="1">
       <c r="A344" s="7" t="inlineStr">
@@ -14037,6 +16001,12 @@
       <c r="L344" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M344" s="9" t="n">
+        <v>345</v>
+      </c>
+      <c r="N344" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="345" ht="15" customHeight="1">
       <c r="A345" s="7" t="inlineStr">
@@ -14081,6 +16051,8 @@
       <c r="L345" s="9" t="n">
         <v>6</v>
       </c>
+      <c r="M345" s="9" t="n"/>
+      <c r="N345" s="9" t="n"/>
     </row>
     <row r="346" ht="15" customHeight="1">
       <c r="A346" s="7" t="inlineStr">
@@ -14121,6 +16093,12 @@
       <c r="L346" s="9" t="n">
         <v>10</v>
       </c>
+      <c r="M346" s="9" t="n">
+        <v>289</v>
+      </c>
+      <c r="N346" s="9" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="347" ht="15" customHeight="1">
       <c r="A347" s="7" t="inlineStr">
@@ -14161,6 +16139,12 @@
       <c r="L347" s="9" t="n">
         <v>12</v>
       </c>
+      <c r="M347" s="9" t="n">
+        <v>73</v>
+      </c>
+      <c r="N347" s="9" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="348" ht="15" customHeight="1">
       <c r="A348" s="7" t="inlineStr">
@@ -14201,6 +16185,12 @@
       <c r="L348" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M348" s="9" t="n">
+        <v>164</v>
+      </c>
+      <c r="N348" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="349" ht="15" customHeight="1">
       <c r="A349" s="7" t="inlineStr">
@@ -14241,6 +16231,12 @@
       <c r="L349" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M349" s="9" t="n">
+        <v>796</v>
+      </c>
+      <c r="N349" s="9" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="350" ht="15" customHeight="1">
       <c r="A350" s="7" t="inlineStr">
@@ -14281,6 +16277,12 @@
       <c r="L350" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M350" s="9" t="n">
+        <v>470</v>
+      </c>
+      <c r="N350" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="351" ht="15" customHeight="1">
       <c r="A351" s="7" t="inlineStr">
@@ -14321,6 +16323,12 @@
       <c r="L351" s="9" t="n">
         <v>11</v>
       </c>
+      <c r="M351" s="9" t="n">
+        <v>330</v>
+      </c>
+      <c r="N351" s="9" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="352" ht="15" customHeight="1">
       <c r="A352" s="7" t="inlineStr">
@@ -14361,6 +16369,12 @@
       <c r="L352" s="9" t="n">
         <v>12</v>
       </c>
+      <c r="M352" s="9" t="n">
+        <v>2159</v>
+      </c>
+      <c r="N352" s="9" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="353" ht="15" customHeight="1">
       <c r="A353" s="7" t="inlineStr">
@@ -14401,6 +16415,12 @@
       <c r="L353" s="9" t="n">
         <v>14</v>
       </c>
+      <c r="M353" s="9" t="n">
+        <v>722</v>
+      </c>
+      <c r="N353" s="9" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="354" ht="15" customHeight="1">
       <c r="A354" s="7" t="inlineStr">
@@ -14441,6 +16461,12 @@
       <c r="L354" s="9" t="n">
         <v>24</v>
       </c>
+      <c r="M354" s="9" t="n">
+        <v>2256</v>
+      </c>
+      <c r="N354" s="9" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="355" ht="15" customHeight="1">
       <c r="A355" s="7" t="inlineStr">
@@ -14481,6 +16507,12 @@
       <c r="L355" s="9" t="n">
         <v>13</v>
       </c>
+      <c r="M355" s="9" t="n">
+        <v>71</v>
+      </c>
+      <c r="N355" s="9" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="356" ht="15" customHeight="1">
       <c r="A356" s="7" t="inlineStr">
@@ -14521,6 +16553,12 @@
       <c r="L356" s="9" t="n">
         <v>16</v>
       </c>
+      <c r="M356" s="9" t="n">
+        <v>117</v>
+      </c>
+      <c r="N356" s="9" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="357" ht="15" customHeight="1">
       <c r="A357" s="7" t="inlineStr">
@@ -14559,6 +16597,12 @@
         <v>2332</v>
       </c>
       <c r="L357" s="9" t="n">
+        <v>19</v>
+      </c>
+      <c r="M357" s="9" t="n">
+        <v>2351</v>
+      </c>
+      <c r="N357" s="9" t="n">
         <v>19</v>
       </c>
     </row>
@@ -14591,6 +16635,8 @@
       <c r="J358" s="9" t="n"/>
       <c r="K358" s="9" t="n"/>
       <c r="L358" s="9" t="n"/>
+      <c r="M358" s="9" t="n"/>
+      <c r="N358" s="9" t="n"/>
     </row>
     <row r="359" ht="15" customHeight="1">
       <c r="A359" s="7" t="inlineStr">
@@ -14631,6 +16677,12 @@
       <c r="L359" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M359" s="9" t="n">
+        <v>196</v>
+      </c>
+      <c r="N359" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="360" ht="15" customHeight="1">
       <c r="A360" s="7" t="inlineStr">
@@ -14671,6 +16723,12 @@
       <c r="L360" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M360" s="9" t="n">
+        <v>349</v>
+      </c>
+      <c r="N360" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="361" ht="15" customHeight="1">
       <c r="A361" s="7" t="inlineStr">
@@ -14711,6 +16769,12 @@
       <c r="L361" s="9" t="n">
         <v>8</v>
       </c>
+      <c r="M361" s="9" t="n">
+        <v>859</v>
+      </c>
+      <c r="N361" s="9" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="362" ht="15" customHeight="1">
       <c r="A362" s="7" t="inlineStr">
@@ -14746,10 +16810,16 @@
         <v>5</v>
       </c>
       <c r="K362" s="9" t="n">
-        <v>1840</v>
+        <v>1835</v>
       </c>
       <c r="L362" s="9" t="n">
         <v>10</v>
+      </c>
+      <c r="M362" s="9" t="n">
+        <v>1839</v>
+      </c>
+      <c r="N362" s="9" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="363" ht="15" customHeight="1">
@@ -14791,6 +16861,12 @@
       <c r="L363" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M363" s="9" t="n">
+        <v>1425</v>
+      </c>
+      <c r="N363" s="9" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="364" ht="15" customHeight="1">
       <c r="A364" s="7" t="inlineStr">
@@ -14831,6 +16907,12 @@
       <c r="L364" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M364" s="9" t="n">
+        <v>66</v>
+      </c>
+      <c r="N364" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="365" ht="15" customHeight="1">
       <c r="A365" s="7" t="inlineStr">
@@ -14870,6 +16952,12 @@
       </c>
       <c r="L365" s="9" t="n">
         <v>7</v>
+      </c>
+      <c r="M365" s="9" t="n">
+        <v>4574</v>
+      </c>
+      <c r="N365" s="9" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="366" ht="15" customHeight="1">
@@ -14905,6 +16993,8 @@
       <c r="J366" s="9" t="n"/>
       <c r="K366" s="9" t="n"/>
       <c r="L366" s="9" t="n"/>
+      <c r="M366" s="9" t="n"/>
+      <c r="N366" s="9" t="n"/>
     </row>
     <row r="367" ht="15" customHeight="1">
       <c r="A367" s="7" t="inlineStr">
@@ -14945,6 +17035,12 @@
       <c r="L367" s="9" t="n">
         <v>8</v>
       </c>
+      <c r="M367" s="9" t="n">
+        <v>1617</v>
+      </c>
+      <c r="N367" s="9" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="368" ht="15" customHeight="1">
       <c r="A368" s="7" t="inlineStr">
@@ -14984,6 +17080,12 @@
       </c>
       <c r="L368" s="9" t="n">
         <v>11</v>
+      </c>
+      <c r="M368" s="9" t="n">
+        <v>2745</v>
+      </c>
+      <c r="N368" s="9" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="369" ht="15" customHeight="1">
@@ -15015,6 +17117,8 @@
       <c r="J369" s="9" t="n"/>
       <c r="K369" s="9" t="n"/>
       <c r="L369" s="9" t="n"/>
+      <c r="M369" s="9" t="n"/>
+      <c r="N369" s="9" t="n"/>
     </row>
     <row r="370" ht="15" customHeight="1">
       <c r="A370" s="7" t="inlineStr">
@@ -15055,6 +17159,12 @@
       <c r="L370" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M370" s="9" t="n">
+        <v>208</v>
+      </c>
+      <c r="N370" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="371" ht="15" customHeight="1">
       <c r="A371" s="7" t="inlineStr">
@@ -15095,6 +17205,12 @@
       <c r="L371" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M371" s="9" t="n">
+        <v>1454</v>
+      </c>
+      <c r="N371" s="9" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="372" ht="15" customHeight="1">
       <c r="A372" s="7" t="inlineStr">
@@ -15130,9 +17246,15 @@
         <v>5</v>
       </c>
       <c r="K372" s="9" t="n">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="L372" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="M372" s="9" t="n">
+        <v>372</v>
+      </c>
+      <c r="N372" s="9" t="n">
         <v>5</v>
       </c>
     </row>
@@ -15175,6 +17297,12 @@
       <c r="L373" s="9" t="n">
         <v>49</v>
       </c>
+      <c r="M373" s="9" t="n">
+        <v>369</v>
+      </c>
+      <c r="N373" s="9" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="374" ht="15" customHeight="1">
       <c r="A374" s="7" t="inlineStr">
@@ -15215,6 +17343,12 @@
       <c r="L374" s="9" t="n">
         <v>15</v>
       </c>
+      <c r="M374" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="N374" s="9" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="375" ht="15" customHeight="1">
       <c r="A375" s="7" t="inlineStr">
@@ -15255,6 +17389,12 @@
       <c r="L375" s="9" t="n">
         <v>11</v>
       </c>
+      <c r="M375" s="9" t="n">
+        <v>71</v>
+      </c>
+      <c r="N375" s="9" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="376" ht="15" customHeight="1">
       <c r="A376" s="7" t="inlineStr">
@@ -15295,6 +17435,12 @@
       <c r="L376" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M376" s="9" t="n">
+        <v>601</v>
+      </c>
+      <c r="N376" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="377" ht="15" customHeight="1">
       <c r="A377" s="7" t="inlineStr">
@@ -15335,6 +17481,12 @@
       <c r="L377" s="9" t="n">
         <v>16</v>
       </c>
+      <c r="M377" s="9" t="n">
+        <v>316</v>
+      </c>
+      <c r="N377" s="9" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="378" ht="15" customHeight="1">
       <c r="A378" s="7" t="inlineStr">
@@ -15370,10 +17522,16 @@
         <v>5</v>
       </c>
       <c r="K378" s="9" t="n">
-        <v>524</v>
+        <v>516</v>
       </c>
       <c r="L378" s="9" t="n">
         <v>11</v>
+      </c>
+      <c r="M378" s="9" t="n">
+        <v>517</v>
+      </c>
+      <c r="N378" s="9" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="379" ht="15" customHeight="1">
@@ -15405,6 +17563,8 @@
       <c r="J379" s="9" t="n"/>
       <c r="K379" s="9" t="n"/>
       <c r="L379" s="9" t="n"/>
+      <c r="M379" s="9" t="n"/>
+      <c r="N379" s="9" t="n"/>
     </row>
     <row r="380" ht="15" customHeight="1">
       <c r="A380" s="7" t="inlineStr">
@@ -15445,6 +17605,12 @@
       <c r="L380" s="9" t="n">
         <v>7</v>
       </c>
+      <c r="M380" s="9" t="n">
+        <v>87</v>
+      </c>
+      <c r="N380" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="381" ht="15" customHeight="1">
       <c r="A381" s="7" t="inlineStr">
@@ -15485,6 +17651,12 @@
       <c r="L381" s="9" t="n">
         <v>14</v>
       </c>
+      <c r="M381" s="9" t="n">
+        <v>59</v>
+      </c>
+      <c r="N381" s="9" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="382" ht="15" customHeight="1">
       <c r="A382" s="7" t="inlineStr">
@@ -15525,6 +17697,12 @@
       <c r="L382" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M382" s="9" t="n">
+        <v>375</v>
+      </c>
+      <c r="N382" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="383" ht="15" customHeight="1">
       <c r="A383" s="7" t="inlineStr">
@@ -15565,6 +17743,12 @@
       <c r="L383" s="9" t="n">
         <v>12</v>
       </c>
+      <c r="M383" s="9" t="n">
+        <v>189</v>
+      </c>
+      <c r="N383" s="9" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="384" ht="15" customHeight="1">
       <c r="A384" s="7" t="inlineStr">
@@ -15605,6 +17789,12 @@
       <c r="L384" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M384" s="9" t="n">
+        <v>2403</v>
+      </c>
+      <c r="N384" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="385" ht="15" customHeight="1">
       <c r="A385" s="7" t="inlineStr">
@@ -15645,6 +17835,12 @@
       <c r="L385" s="9" t="n">
         <v>14</v>
       </c>
+      <c r="M385" s="9" t="n">
+        <v>1839</v>
+      </c>
+      <c r="N385" s="9" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="386" ht="15" customHeight="1">
       <c r="A386" s="7" t="inlineStr">
@@ -15685,6 +17881,12 @@
       <c r="L386" s="9" t="n">
         <v>14</v>
       </c>
+      <c r="M386" s="9" t="n">
+        <v>491</v>
+      </c>
+      <c r="N386" s="9" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="387" ht="15" customHeight="1">
       <c r="A387" s="7" t="inlineStr">
@@ -15725,6 +17927,12 @@
       <c r="L387" s="9" t="n">
         <v>53</v>
       </c>
+      <c r="M387" s="9" t="n">
+        <v>562</v>
+      </c>
+      <c r="N387" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="388" ht="15" customHeight="1">
       <c r="A388" s="7" t="inlineStr">
@@ -15765,6 +17973,12 @@
       <c r="L388" s="9" t="n">
         <v>6</v>
       </c>
+      <c r="M388" s="9" t="n">
+        <v>2212</v>
+      </c>
+      <c r="N388" s="9" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="389" ht="15" customHeight="1">
       <c r="A389" s="7" t="inlineStr">
@@ -15805,6 +18019,12 @@
       <c r="L389" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M389" s="9" t="n">
+        <v>401</v>
+      </c>
+      <c r="N389" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="390" ht="15" customHeight="1">
       <c r="A390" s="7" t="inlineStr">
@@ -15845,6 +18065,12 @@
       <c r="L390" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M390" s="9" t="n">
+        <v>1066</v>
+      </c>
+      <c r="N390" s="9" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="391" ht="15" customHeight="1">
       <c r="A391" s="7" t="inlineStr">
@@ -15885,6 +18111,12 @@
       <c r="L391" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M391" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="N391" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="392" ht="15" customHeight="1">
       <c r="A392" s="7" t="inlineStr">
@@ -15925,6 +18157,12 @@
       <c r="L392" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M392" s="9" t="n">
+        <v>7213</v>
+      </c>
+      <c r="N392" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="393" ht="15" customHeight="1">
       <c r="A393" s="7" t="inlineStr">
@@ -15965,6 +18203,12 @@
       <c r="L393" s="9" t="n">
         <v>11</v>
       </c>
+      <c r="M393" s="9" t="n">
+        <v>1573</v>
+      </c>
+      <c r="N393" s="9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="394" ht="15" customHeight="1">
       <c r="A394" s="7" t="inlineStr">
@@ -16005,6 +18249,12 @@
       <c r="L394" s="9" t="n">
         <v>18</v>
       </c>
+      <c r="M394" s="9" t="n">
+        <v>1213</v>
+      </c>
+      <c r="N394" s="9" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="395" ht="15" customHeight="1">
       <c r="A395" s="7" t="inlineStr">
@@ -16045,6 +18295,12 @@
       <c r="L395" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M395" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="N395" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="396" ht="15" customHeight="1">
       <c r="A396" s="7" t="inlineStr">
@@ -16085,6 +18341,12 @@
       <c r="L396" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M396" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="N396" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="397" ht="15" customHeight="1">
       <c r="A397" s="7" t="inlineStr">
@@ -16125,6 +18387,12 @@
       <c r="L397" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M397" s="9" t="n">
+        <v>300</v>
+      </c>
+      <c r="N397" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="398" ht="15" customHeight="1">
       <c r="A398" s="7" t="inlineStr">
@@ -16165,6 +18433,12 @@
       <c r="L398" s="9" t="n">
         <v>16</v>
       </c>
+      <c r="M398" s="9" t="n">
+        <v>1140</v>
+      </c>
+      <c r="N398" s="9" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="399" ht="15" customHeight="1">
       <c r="A399" s="7" t="inlineStr">
@@ -16205,6 +18479,12 @@
       <c r="L399" s="9" t="n">
         <v>14</v>
       </c>
+      <c r="M399" s="9" t="n">
+        <v>2126</v>
+      </c>
+      <c r="N399" s="9" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="400" ht="15" customHeight="1">
       <c r="A400" s="7" t="inlineStr">
@@ -16245,6 +18525,12 @@
       <c r="L400" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M400" s="9" t="n">
+        <v>1089</v>
+      </c>
+      <c r="N400" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="401" ht="15" customHeight="1">
       <c r="A401" s="7" t="inlineStr">
@@ -16285,6 +18571,12 @@
       <c r="L401" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M401" s="9" t="n">
+        <v>559</v>
+      </c>
+      <c r="N401" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="402" ht="15" customHeight="1">
       <c r="A402" s="7" t="inlineStr">
@@ -16325,6 +18617,12 @@
       <c r="L402" s="9" t="n">
         <v>22</v>
       </c>
+      <c r="M402" s="9" t="n">
+        <v>1036</v>
+      </c>
+      <c r="N402" s="9" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="403" ht="15" customHeight="1">
       <c r="A403" s="7" t="inlineStr">
@@ -16365,6 +18663,12 @@
       <c r="L403" s="9" t="n">
         <v>16</v>
       </c>
+      <c r="M403" s="9" t="n">
+        <v>2552</v>
+      </c>
+      <c r="N403" s="9" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="404" ht="15" customHeight="1">
       <c r="A404" s="7" t="inlineStr">
@@ -16405,6 +18709,12 @@
       <c r="L404" s="9" t="n">
         <v>15</v>
       </c>
+      <c r="M404" s="9" t="n">
+        <v>1574</v>
+      </c>
+      <c r="N404" s="9" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="405" ht="15" customHeight="1">
       <c r="A405" s="7" t="inlineStr">
@@ -16445,6 +18755,12 @@
       <c r="L405" s="9" t="n">
         <v>9</v>
       </c>
+      <c r="M405" s="9" t="n">
+        <v>2513</v>
+      </c>
+      <c r="N405" s="9" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="406" ht="15" customHeight="1">
       <c r="A406" s="7" t="inlineStr">
@@ -16485,6 +18801,12 @@
       <c r="L406" s="9" t="n">
         <v>12</v>
       </c>
+      <c r="M406" s="9" t="n">
+        <v>162</v>
+      </c>
+      <c r="N406" s="9" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="407" ht="15" customHeight="1">
       <c r="A407" s="7" t="inlineStr">
@@ -16525,6 +18847,12 @@
       <c r="L407" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M407" s="9" t="n">
+        <v>225</v>
+      </c>
+      <c r="N407" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="408" ht="15" customHeight="1">
       <c r="A408" s="7" t="inlineStr">
@@ -16565,6 +18893,12 @@
       <c r="L408" s="9" t="n">
         <v>6</v>
       </c>
+      <c r="M408" s="9" t="n">
+        <v>1020</v>
+      </c>
+      <c r="N408" s="9" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="409" ht="15" customHeight="1">
       <c r="A409" s="7" t="inlineStr">
@@ -16605,6 +18939,12 @@
       <c r="L409" s="9" t="n">
         <v>14</v>
       </c>
+      <c r="M409" s="9" t="n">
+        <v>145</v>
+      </c>
+      <c r="N409" s="9" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="410" ht="15" customHeight="1">
       <c r="A410" s="7" t="inlineStr">
@@ -16645,6 +18985,12 @@
       <c r="L410" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M410" s="9" t="n">
+        <v>29</v>
+      </c>
+      <c r="N410" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="411" ht="15" customHeight="1">
       <c r="A411" s="7" t="inlineStr">
@@ -16685,6 +19031,12 @@
       <c r="L411" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M411" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="N411" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="412" ht="15" customHeight="1">
       <c r="A412" s="7" t="inlineStr">
@@ -16725,6 +19077,12 @@
       <c r="L412" s="9" t="n">
         <v>8</v>
       </c>
+      <c r="M412" s="9" t="n">
+        <v>48</v>
+      </c>
+      <c r="N412" s="9" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="413" ht="15" customHeight="1">
       <c r="A413" s="7" t="inlineStr">
@@ -16765,6 +19123,12 @@
       <c r="L413" s="9" t="n">
         <v>21</v>
       </c>
+      <c r="M413" s="9" t="n">
+        <v>111</v>
+      </c>
+      <c r="N413" s="9" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="414" ht="15" customHeight="1">
       <c r="A414" s="7" t="inlineStr">
@@ -16805,6 +19169,12 @@
       <c r="L414" s="9" t="n">
         <v>13</v>
       </c>
+      <c r="M414" s="9" t="n">
+        <v>89</v>
+      </c>
+      <c r="N414" s="9" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="415" ht="15" customHeight="1">
       <c r="A415" s="7" t="inlineStr">
@@ -16840,9 +19210,15 @@
         <v>5</v>
       </c>
       <c r="K415" s="9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L415" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="M415" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="N415" s="9" t="n">
         <v>5</v>
       </c>
     </row>
@@ -16883,6 +19259,12 @@
         <v>369</v>
       </c>
       <c r="L416" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="M416" s="9" t="n">
+        <v>371</v>
+      </c>
+      <c r="N416" s="9" t="n">
         <v>5</v>
       </c>
     </row>
@@ -16915,6 +19297,8 @@
       <c r="J417" s="9" t="n"/>
       <c r="K417" s="9" t="n"/>
       <c r="L417" s="9" t="n"/>
+      <c r="M417" s="9" t="n"/>
+      <c r="N417" s="9" t="n"/>
     </row>
     <row r="418" ht="15" customHeight="1">
       <c r="A418" s="7" t="inlineStr">
@@ -16953,6 +19337,12 @@
         <v>0</v>
       </c>
       <c r="L418" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="M418" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N418" s="9" t="n">
         <v>5</v>
       </c>
     </row>
@@ -16985,6 +19375,8 @@
       <c r="J419" s="9" t="n"/>
       <c r="K419" s="9" t="n"/>
       <c r="L419" s="9" t="n"/>
+      <c r="M419" s="9" t="n"/>
+      <c r="N419" s="9" t="n"/>
     </row>
     <row r="420" ht="15" customHeight="1">
       <c r="A420" s="7" t="inlineStr">
@@ -17015,6 +19407,8 @@
       <c r="J420" s="9" t="n"/>
       <c r="K420" s="9" t="n"/>
       <c r="L420" s="9" t="n"/>
+      <c r="M420" s="9" t="n"/>
+      <c r="N420" s="9" t="n"/>
     </row>
     <row r="421" ht="15" customHeight="1">
       <c r="A421" s="7" t="inlineStr">
@@ -17055,6 +19449,12 @@
       <c r="L421" s="9" t="n">
         <v>6</v>
       </c>
+      <c r="M421" s="9" t="n">
+        <v>691</v>
+      </c>
+      <c r="N421" s="9" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="422" ht="15" customHeight="1">
       <c r="A422" s="7" t="inlineStr">
@@ -17093,6 +19493,12 @@
         <v>44</v>
       </c>
       <c r="L422" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="M422" s="9" t="n">
+        <v>49</v>
+      </c>
+      <c r="N422" s="9" t="n">
         <v>5</v>
       </c>
     </row>
@@ -17125,6 +19531,8 @@
       <c r="J423" s="9" t="n"/>
       <c r="K423" s="9" t="n"/>
       <c r="L423" s="9" t="n"/>
+      <c r="M423" s="9" t="n"/>
+      <c r="N423" s="9" t="n"/>
     </row>
     <row r="424" ht="15" customHeight="1">
       <c r="A424" s="7" t="inlineStr">
@@ -17165,6 +19573,12 @@
       <c r="L424" s="9" t="n">
         <v>19</v>
       </c>
+      <c r="M424" s="9" t="n">
+        <v>3739</v>
+      </c>
+      <c r="N424" s="9" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="425" ht="15" customHeight="1">
       <c r="A425" s="7" t="inlineStr">
@@ -17204,6 +19618,12 @@
       </c>
       <c r="L425" s="9" t="n">
         <v>7</v>
+      </c>
+      <c r="M425" s="9" t="n">
+        <v>2298</v>
+      </c>
+      <c r="N425" s="9" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="426" ht="15" customHeight="1">
@@ -17235,6 +19655,8 @@
       <c r="J426" s="9" t="n"/>
       <c r="K426" s="9" t="n"/>
       <c r="L426" s="9" t="n"/>
+      <c r="M426" s="9" t="n"/>
+      <c r="N426" s="9" t="n"/>
     </row>
     <row r="427" ht="15" customHeight="1">
       <c r="A427" s="7" t="inlineStr">
@@ -17275,6 +19697,12 @@
       <c r="L427" s="9" t="n">
         <v>12</v>
       </c>
+      <c r="M427" s="9" t="n">
+        <v>2390</v>
+      </c>
+      <c r="N427" s="9" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="428" ht="15" customHeight="1">
       <c r="A428" s="7" t="inlineStr">
@@ -17315,6 +19743,12 @@
       <c r="L428" s="9" t="n">
         <v>15</v>
       </c>
+      <c r="M428" s="9" t="n">
+        <v>1235</v>
+      </c>
+      <c r="N428" s="9" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="429" ht="15" customHeight="1">
       <c r="A429" s="7" t="inlineStr">
@@ -17355,6 +19789,12 @@
       <c r="L429" s="9" t="n">
         <v>13</v>
       </c>
+      <c r="M429" s="9" t="n">
+        <v>278</v>
+      </c>
+      <c r="N429" s="9" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="430" ht="15" customHeight="1">
       <c r="A430" s="7" t="inlineStr">
@@ -17395,6 +19835,12 @@
       <c r="L430" s="9" t="n">
         <v>15</v>
       </c>
+      <c r="M430" s="9" t="n">
+        <v>1783</v>
+      </c>
+      <c r="N430" s="9" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="431" ht="15" customHeight="1">
       <c r="A431" s="7" t="inlineStr">
@@ -17435,6 +19881,12 @@
       <c r="L431" s="9" t="n">
         <v>14</v>
       </c>
+      <c r="M431" s="9" t="n">
+        <v>805</v>
+      </c>
+      <c r="N431" s="9" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="432" ht="15" customHeight="1">
       <c r="A432" s="7" t="inlineStr">
@@ -17473,6 +19925,12 @@
         <v>3322</v>
       </c>
       <c r="L432" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="M432" s="9" t="n">
+        <v>3331</v>
+      </c>
+      <c r="N432" s="9" t="n">
         <v>9</v>
       </c>
     </row>
@@ -17505,6 +19963,8 @@
       <c r="J433" s="9" t="n"/>
       <c r="K433" s="9" t="n"/>
       <c r="L433" s="9" t="n"/>
+      <c r="M433" s="9" t="n"/>
+      <c r="N433" s="9" t="n"/>
     </row>
     <row r="434" ht="15" customHeight="1">
       <c r="A434" s="7" t="inlineStr">
@@ -17545,6 +20005,12 @@
       <c r="L434" s="9" t="n">
         <v>13</v>
       </c>
+      <c r="M434" s="9" t="n">
+        <v>2608</v>
+      </c>
+      <c r="N434" s="9" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="435" ht="15" customHeight="1">
       <c r="A435" s="7" t="inlineStr">
@@ -17583,6 +20049,12 @@
         <v>225</v>
       </c>
       <c r="L435" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="M435" s="9" t="n">
+        <v>226</v>
+      </c>
+      <c r="N435" s="9" t="n">
         <v>5</v>
       </c>
     </row>
@@ -17615,6 +20087,8 @@
       <c r="J436" s="9" t="n"/>
       <c r="K436" s="9" t="n"/>
       <c r="L436" s="9" t="n"/>
+      <c r="M436" s="9" t="n"/>
+      <c r="N436" s="9" t="n"/>
     </row>
     <row r="437" ht="15" customHeight="1">
       <c r="A437" s="7" t="inlineStr">
@@ -17629,7 +20103,7 @@
       </c>
       <c r="C437" s="8" t="inlineStr">
         <is>
-          <t>ELVIRA MINAYA LOZANO</t>
+          <t>ELVIRA LOZANO MINAYA</t>
         </is>
       </c>
       <c r="D437" s="7" t="n"/>
@@ -17655,6 +20129,12 @@
       <c r="L437" s="9" t="n">
         <v>12</v>
       </c>
+      <c r="M437" s="9" t="n">
+        <v>772</v>
+      </c>
+      <c r="N437" s="9" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="438" ht="15" customHeight="1">
       <c r="A438" s="7" t="inlineStr">
@@ -17695,6 +20175,12 @@
       <c r="L438" s="9" t="n">
         <v>15</v>
       </c>
+      <c r="M438" s="9" t="n">
+        <v>632</v>
+      </c>
+      <c r="N438" s="9" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="439" ht="15" customHeight="1">
       <c r="A439" s="7" t="inlineStr">
@@ -17735,6 +20221,12 @@
       <c r="L439" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M439" s="9" t="n">
+        <v>132</v>
+      </c>
+      <c r="N439" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="440" ht="15" customHeight="1">
       <c r="A440" s="7" t="inlineStr">
@@ -17775,6 +20267,12 @@
       <c r="L440" s="9" t="n">
         <v>6</v>
       </c>
+      <c r="M440" s="9" t="n">
+        <v>1204</v>
+      </c>
+      <c r="N440" s="9" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="441" ht="15" customHeight="1">
       <c r="A441" s="7" t="inlineStr">
@@ -17815,6 +20313,12 @@
       <c r="L441" s="9" t="n">
         <v>9</v>
       </c>
+      <c r="M441" s="9" t="n">
+        <v>1027</v>
+      </c>
+      <c r="N441" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="442" ht="15" customHeight="1">
       <c r="A442" s="7" t="inlineStr">
@@ -17854,6 +20358,12 @@
       </c>
       <c r="L442" s="9" t="n">
         <v>9</v>
+      </c>
+      <c r="M442" s="9" t="n">
+        <v>229</v>
+      </c>
+      <c r="N442" s="9" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="443" ht="15" customHeight="1">
@@ -17885,6 +20395,8 @@
       <c r="J443" s="9" t="n"/>
       <c r="K443" s="9" t="n"/>
       <c r="L443" s="9" t="n"/>
+      <c r="M443" s="9" t="n"/>
+      <c r="N443" s="9" t="n"/>
     </row>
     <row r="444" ht="15" customHeight="1">
       <c r="A444" s="7" t="inlineStr">
@@ -17915,6 +20427,8 @@
       <c r="J444" s="9" t="n"/>
       <c r="K444" s="9" t="n"/>
       <c r="L444" s="9" t="n"/>
+      <c r="M444" s="9" t="n"/>
+      <c r="N444" s="9" t="n"/>
     </row>
     <row r="445" ht="15" customHeight="1">
       <c r="A445" s="7" t="inlineStr">
@@ -17955,6 +20469,12 @@
       <c r="L445" s="9" t="n">
         <v>6</v>
       </c>
+      <c r="M445" s="9" t="n">
+        <v>1374</v>
+      </c>
+      <c r="N445" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="446" ht="15" customHeight="1">
       <c r="A446" s="7" t="inlineStr">
@@ -17995,6 +20515,12 @@
       <c r="L446" s="9" t="n">
         <v>6</v>
       </c>
+      <c r="M446" s="9" t="n">
+        <v>102</v>
+      </c>
+      <c r="N446" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="447" ht="15" customHeight="1">
       <c r="A447" s="7" t="inlineStr">
@@ -18035,6 +20561,12 @@
       <c r="L447" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M447" s="9" t="n">
+        <v>47</v>
+      </c>
+      <c r="N447" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="448" ht="15" customHeight="1">
       <c r="A448" s="7" t="inlineStr">
@@ -18075,6 +20607,12 @@
       <c r="L448" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M448" s="9" t="n">
+        <v>307</v>
+      </c>
+      <c r="N448" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="449" ht="15" customHeight="1">
       <c r="A449" s="7" t="inlineStr">
@@ -18115,6 +20653,12 @@
       <c r="L449" s="9" t="n">
         <v>11</v>
       </c>
+      <c r="M449" s="9" t="n">
+        <v>897</v>
+      </c>
+      <c r="N449" s="9" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="450" ht="15" customHeight="1">
       <c r="A450" s="7" t="inlineStr">
@@ -18155,6 +20699,12 @@
       <c r="L450" s="9" t="n">
         <v>12</v>
       </c>
+      <c r="M450" s="9" t="n">
+        <v>1698</v>
+      </c>
+      <c r="N450" s="9" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="451" ht="15" customHeight="1">
       <c r="A451" s="7" t="inlineStr">
@@ -18195,6 +20745,12 @@
       <c r="L451" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M451" s="9" t="n">
+        <v>33</v>
+      </c>
+      <c r="N451" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="452" ht="15" customHeight="1">
       <c r="A452" s="7" t="inlineStr">
@@ -18234,6 +20790,12 @@
       </c>
       <c r="L452" s="9" t="n">
         <v>13</v>
+      </c>
+      <c r="M452" s="9" t="n">
+        <v>128</v>
+      </c>
+      <c r="N452" s="9" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="453" ht="15" customHeight="1">
@@ -18265,6 +20827,8 @@
       <c r="J453" s="9" t="n"/>
       <c r="K453" s="9" t="n"/>
       <c r="L453" s="9" t="n"/>
+      <c r="M453" s="9" t="n"/>
+      <c r="N453" s="9" t="n"/>
     </row>
     <row r="454" ht="15" customHeight="1">
       <c r="A454" s="7" t="inlineStr">
@@ -18303,6 +20867,12 @@
         <v>264</v>
       </c>
       <c r="L454" s="9" t="n"/>
+      <c r="M454" s="9" t="n">
+        <v>264</v>
+      </c>
+      <c r="N454" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="455" ht="15" customHeight="1">
       <c r="A455" s="7" t="inlineStr">
@@ -18341,6 +20911,12 @@
         <v>1447</v>
       </c>
       <c r="L455" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="M455" s="9" t="n">
+        <v>1465</v>
+      </c>
+      <c r="N455" s="9" t="n">
         <v>18</v>
       </c>
     </row>
@@ -18373,6 +20949,8 @@
       <c r="J456" s="9" t="n"/>
       <c r="K456" s="9" t="n"/>
       <c r="L456" s="9" t="n"/>
+      <c r="M456" s="9" t="n"/>
+      <c r="N456" s="9" t="n"/>
     </row>
     <row r="457" ht="15" customHeight="1">
       <c r="A457" s="7" t="inlineStr">
@@ -18413,6 +20991,12 @@
       <c r="L457" s="9" t="n">
         <v>14</v>
       </c>
+      <c r="M457" s="9" t="n">
+        <v>1242</v>
+      </c>
+      <c r="N457" s="9" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="458" ht="15" customHeight="1">
       <c r="A458" s="7" t="inlineStr">
@@ -18451,6 +21035,12 @@
         <v>1035</v>
       </c>
       <c r="L458" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="M458" s="9" t="n">
+        <v>1045</v>
+      </c>
+      <c r="N458" s="9" t="n">
         <v>10</v>
       </c>
     </row>
@@ -18483,6 +21073,8 @@
       <c r="J459" s="9" t="n"/>
       <c r="K459" s="9" t="n"/>
       <c r="L459" s="9" t="n"/>
+      <c r="M459" s="9" t="n"/>
+      <c r="N459" s="9" t="n"/>
     </row>
     <row r="460" ht="15" customHeight="1">
       <c r="A460" s="7" t="inlineStr">
@@ -18523,6 +21115,12 @@
       <c r="L460" s="9" t="n">
         <v>14</v>
       </c>
+      <c r="M460" s="9" t="n">
+        <v>1610</v>
+      </c>
+      <c r="N460" s="9" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="461" ht="15" customHeight="1">
       <c r="A461" s="7" t="inlineStr">
@@ -18563,6 +21161,12 @@
       <c r="L461" s="9" t="n">
         <v>7</v>
       </c>
+      <c r="M461" s="9" t="n">
+        <v>521</v>
+      </c>
+      <c r="N461" s="9" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="462" ht="15" customHeight="1">
       <c r="A462" s="7" t="inlineStr">
@@ -18603,6 +21207,12 @@
       <c r="L462" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M462" s="9" t="n">
+        <v>2002</v>
+      </c>
+      <c r="N462" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="463" ht="15" customHeight="1">
       <c r="A463" s="7" t="inlineStr">
@@ -18643,6 +21253,12 @@
       <c r="L463" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M463" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="N463" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="464" ht="15" customHeight="1">
       <c r="A464" s="7" t="inlineStr">
@@ -18683,6 +21299,12 @@
       <c r="L464" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M464" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N464" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="465" ht="15" customHeight="1">
       <c r="A465" s="7" t="inlineStr">
@@ -18723,6 +21345,12 @@
       <c r="L465" s="9" t="n">
         <v>6</v>
       </c>
+      <c r="M465" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="N465" s="9" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="466" ht="15" customHeight="1">
       <c r="A466" s="7" t="inlineStr">
@@ -18763,6 +21391,12 @@
       <c r="L466" s="9" t="n">
         <v>11</v>
       </c>
+      <c r="M466" s="9" t="n">
+        <v>489</v>
+      </c>
+      <c r="N466" s="9" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="467" ht="15" customHeight="1">
       <c r="A467" s="7" t="inlineStr">
@@ -18801,6 +21435,12 @@
         <v>520</v>
       </c>
       <c r="L467" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="M467" s="9" t="n">
+        <v>525</v>
+      </c>
+      <c r="N467" s="9" t="n">
         <v>5</v>
       </c>
     </row>
@@ -18833,6 +21473,8 @@
       <c r="J468" s="9" t="n"/>
       <c r="K468" s="9" t="n"/>
       <c r="L468" s="9" t="n"/>
+      <c r="M468" s="9" t="n"/>
+      <c r="N468" s="9" t="n"/>
     </row>
     <row r="469" ht="15" customHeight="1">
       <c r="A469" s="7" t="inlineStr">
@@ -18873,6 +21515,12 @@
       <c r="L469" s="9" t="n">
         <v>7</v>
       </c>
+      <c r="M469" s="9" t="n">
+        <v>1428</v>
+      </c>
+      <c r="N469" s="9" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="470" ht="15" customHeight="1">
       <c r="A470" s="7" t="inlineStr">
@@ -18913,6 +21561,12 @@
       <c r="L470" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M470" s="9" t="n">
+        <v>95</v>
+      </c>
+      <c r="N470" s="9" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="471" ht="15" customHeight="1">
       <c r="A471" s="7" t="inlineStr">
@@ -18953,6 +21607,12 @@
       <c r="L471" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M471" s="9" t="n">
+        <v>597</v>
+      </c>
+      <c r="N471" s="9" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="472" ht="15" customHeight="1">
       <c r="A472" s="7" t="inlineStr">
@@ -18993,6 +21653,12 @@
       <c r="L472" s="9" t="n">
         <v>10</v>
       </c>
+      <c r="M472" s="9" t="n">
+        <v>1232</v>
+      </c>
+      <c r="N472" s="9" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="473" ht="15" customHeight="1">
       <c r="A473" s="7" t="inlineStr">
@@ -19033,6 +21699,12 @@
       <c r="L473" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M473" s="9" t="n">
+        <v>1541</v>
+      </c>
+      <c r="N473" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="474" ht="15" customHeight="1">
       <c r="A474" s="7" t="inlineStr">
@@ -19073,6 +21745,12 @@
       <c r="L474" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M474" s="9" t="n">
+        <v>1945</v>
+      </c>
+      <c r="N474" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="475" ht="15" customHeight="1">
       <c r="A475" s="7" t="inlineStr">
@@ -19113,6 +21791,12 @@
       <c r="L475" s="9" t="n">
         <v>31</v>
       </c>
+      <c r="M475" s="9" t="n">
+        <v>2155</v>
+      </c>
+      <c r="N475" s="9" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="476" ht="15" customHeight="1">
       <c r="A476" s="7" t="inlineStr">
@@ -19152,6 +21836,12 @@
       </c>
       <c r="L476" s="9" t="n">
         <v>22</v>
+      </c>
+      <c r="M476" s="9" t="n">
+        <v>354</v>
+      </c>
+      <c r="N476" s="9" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="477" ht="15" customHeight="1">
@@ -19187,6 +21877,8 @@
       <c r="L477" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M477" s="9" t="n"/>
+      <c r="N477" s="9" t="n"/>
     </row>
     <row r="478" ht="15" customHeight="1">
       <c r="A478" s="7" t="inlineStr">
@@ -19227,6 +21919,12 @@
       <c r="L478" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M478" s="9" t="n">
+        <v>523</v>
+      </c>
+      <c r="N478" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="479" ht="15" customHeight="1">
       <c r="A479" s="7" t="inlineStr">
@@ -19267,6 +21965,12 @@
       <c r="L479" s="9" t="n">
         <v>21</v>
       </c>
+      <c r="M479" s="9" t="n">
+        <v>1036</v>
+      </c>
+      <c r="N479" s="9" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="480" ht="15" customHeight="1">
       <c r="A480" s="7" t="inlineStr">
@@ -19302,10 +22006,16 @@
         <v>61</v>
       </c>
       <c r="K480" s="9" t="n">
-        <v>7879</v>
+        <v>7827</v>
       </c>
       <c r="L480" s="9" t="n">
         <v>104</v>
+      </c>
+      <c r="M480" s="9" t="n">
+        <v>7878</v>
+      </c>
+      <c r="N480" s="9" t="n">
+        <v>102</v>
       </c>
     </row>
     <row r="481" ht="15" customHeight="1">
@@ -19347,6 +22057,12 @@
       <c r="L481" s="9" t="n">
         <v>8</v>
       </c>
+      <c r="M481" s="9" t="n">
+        <v>321</v>
+      </c>
+      <c r="N481" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="482" ht="15" customHeight="1">
       <c r="A482" s="7" t="inlineStr">
@@ -19387,6 +22103,12 @@
       <c r="L482" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M482" s="9" t="n">
+        <v>1101</v>
+      </c>
+      <c r="N482" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="483" ht="15" customHeight="1">
       <c r="A483" s="7" t="inlineStr">
@@ -19427,6 +22149,12 @@
       <c r="L483" s="9" t="n">
         <v>8</v>
       </c>
+      <c r="M483" s="9" t="n">
+        <v>1253</v>
+      </c>
+      <c r="N483" s="9" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="484" ht="15" customHeight="1">
       <c r="A484" s="7" t="inlineStr">
@@ -19467,6 +22195,12 @@
       <c r="L484" s="9" t="n">
         <v>6</v>
       </c>
+      <c r="M484" s="9" t="n">
+        <v>311</v>
+      </c>
+      <c r="N484" s="9" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="485" ht="15" customHeight="1">
       <c r="A485" s="7" t="inlineStr">
@@ -19506,6 +22240,12 @@
       </c>
       <c r="L485" s="9" t="n">
         <v>10</v>
+      </c>
+      <c r="M485" s="9" t="n">
+        <v>496</v>
+      </c>
+      <c r="N485" s="9" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="486" ht="15" customHeight="1">
@@ -19537,6 +22277,8 @@
       <c r="J486" s="9" t="n"/>
       <c r="K486" s="9" t="n"/>
       <c r="L486" s="9" t="n"/>
+      <c r="M486" s="9" t="n"/>
+      <c r="N486" s="9" t="n"/>
     </row>
     <row r="487" ht="15" customHeight="1">
       <c r="A487" s="7" t="inlineStr">
@@ -19567,6 +22309,8 @@
       <c r="J487" s="9" t="n"/>
       <c r="K487" s="9" t="n"/>
       <c r="L487" s="9" t="n"/>
+      <c r="M487" s="9" t="n"/>
+      <c r="N487" s="9" t="n"/>
     </row>
     <row r="488" ht="15" customHeight="1">
       <c r="A488" s="7" t="inlineStr">
@@ -19597,6 +22341,8 @@
       <c r="J488" s="9" t="n"/>
       <c r="K488" s="9" t="n"/>
       <c r="L488" s="9" t="n"/>
+      <c r="M488" s="9" t="n"/>
+      <c r="N488" s="9" t="n"/>
     </row>
     <row r="489" ht="15" customHeight="1">
       <c r="A489" s="7" t="inlineStr">
@@ -19637,6 +22383,12 @@
       <c r="L489" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M489" s="9" t="n">
+        <v>91</v>
+      </c>
+      <c r="N489" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="490" ht="15" customHeight="1">
       <c r="A490" s="7" t="inlineStr">
@@ -19677,6 +22429,12 @@
       <c r="L490" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M490" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="N490" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="491" ht="15" customHeight="1">
       <c r="A491" s="7" t="inlineStr">
@@ -19691,7 +22449,7 @@
       </c>
       <c r="C491" s="8" t="inlineStr">
         <is>
-          <t>REIMI VILLANUEVA ALEGRIA</t>
+          <t>EPIFANIA CHICHAY LEON</t>
         </is>
       </c>
       <c r="D491" s="7" t="n"/>
@@ -19717,6 +22475,12 @@
       <c r="L491" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M491" s="9" t="n">
+        <v>96</v>
+      </c>
+      <c r="N491" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="492" ht="15" customHeight="1">
       <c r="A492" s="7" t="inlineStr">
@@ -19756,6 +22520,12 @@
       </c>
       <c r="L492" s="9" t="n">
         <v>7</v>
+      </c>
+      <c r="M492" s="9" t="n">
+        <v>1775</v>
+      </c>
+      <c r="N492" s="9" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="493" ht="15" customHeight="1">
@@ -19787,6 +22557,8 @@
       <c r="J493" s="9" t="n"/>
       <c r="K493" s="9" t="n"/>
       <c r="L493" s="9" t="n"/>
+      <c r="M493" s="9" t="n"/>
+      <c r="N493" s="9" t="n"/>
     </row>
     <row r="494" ht="15" customHeight="1">
       <c r="A494" s="7" t="inlineStr">
@@ -19827,6 +22599,12 @@
       <c r="L494" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M494" s="9" t="n">
+        <v>33</v>
+      </c>
+      <c r="N494" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="495" ht="15" customHeight="1">
       <c r="A495" s="7" t="inlineStr">
@@ -19867,6 +22645,12 @@
       <c r="L495" s="9" t="n">
         <v>10</v>
       </c>
+      <c r="M495" s="9" t="n">
+        <v>168</v>
+      </c>
+      <c r="N495" s="9" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="496" ht="15" customHeight="1">
       <c r="A496" s="7" t="inlineStr">
@@ -19907,6 +22691,12 @@
       <c r="L496" s="9" t="n">
         <v>6</v>
       </c>
+      <c r="M496" s="9" t="n">
+        <v>1601</v>
+      </c>
+      <c r="N496" s="9" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="497" ht="15" customHeight="1">
       <c r="A497" s="7" t="inlineStr">
@@ -19945,6 +22735,12 @@
         <v>1156</v>
       </c>
       <c r="L497" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="M497" s="9" t="n">
+        <v>1163</v>
+      </c>
+      <c r="N497" s="9" t="n">
         <v>7</v>
       </c>
     </row>
@@ -19977,6 +22773,8 @@
       <c r="J498" s="9" t="n"/>
       <c r="K498" s="9" t="n"/>
       <c r="L498" s="9" t="n"/>
+      <c r="M498" s="9" t="n"/>
+      <c r="N498" s="9" t="n"/>
     </row>
     <row r="499" ht="15" customHeight="1">
       <c r="A499" s="7" t="inlineStr">
@@ -20017,6 +22815,12 @@
       <c r="L499" s="9" t="n">
         <v>14</v>
       </c>
+      <c r="M499" s="9" t="n">
+        <v>1801</v>
+      </c>
+      <c r="N499" s="9" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="500" ht="15" customHeight="1">
       <c r="A500" s="7" t="inlineStr">
@@ -20057,6 +22861,12 @@
       <c r="L500" s="9" t="n">
         <v>14</v>
       </c>
+      <c r="M500" s="9" t="n">
+        <v>1728</v>
+      </c>
+      <c r="N500" s="9" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="501" ht="15" customHeight="1">
       <c r="A501" s="7" t="inlineStr">
@@ -20097,6 +22907,12 @@
       <c r="L501" s="9" t="n">
         <v>9</v>
       </c>
+      <c r="M501" s="9" t="n">
+        <v>1632</v>
+      </c>
+      <c r="N501" s="9" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="502" ht="15" customHeight="1">
       <c r="A502" s="7" t="inlineStr">
@@ -20137,6 +22953,12 @@
       <c r="L502" s="9" t="n">
         <v>10</v>
       </c>
+      <c r="M502" s="9" t="n">
+        <v>845</v>
+      </c>
+      <c r="N502" s="9" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="503" ht="15" customHeight="1">
       <c r="A503" s="7" t="inlineStr">
@@ -20177,6 +22999,12 @@
       <c r="L503" s="9" t="n">
         <v>14</v>
       </c>
+      <c r="M503" s="9" t="n">
+        <v>1018</v>
+      </c>
+      <c r="N503" s="9" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="504" ht="15" customHeight="1">
       <c r="A504" s="7" t="inlineStr">
@@ -20217,6 +23045,12 @@
       <c r="L504" s="9" t="n">
         <v>13</v>
       </c>
+      <c r="M504" s="9" t="n">
+        <v>210</v>
+      </c>
+      <c r="N504" s="9" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="505" ht="15" customHeight="1">
       <c r="A505" s="7" t="inlineStr">
@@ -20257,6 +23091,12 @@
       <c r="L505" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M505" s="9" t="n">
+        <v>296</v>
+      </c>
+      <c r="N505" s="9" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="506" ht="15" customHeight="1">
       <c r="A506" s="7" t="inlineStr">
@@ -20297,6 +23137,12 @@
       <c r="L506" s="9" t="n">
         <v>11</v>
       </c>
+      <c r="M506" s="9" t="n">
+        <v>1990</v>
+      </c>
+      <c r="N506" s="9" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="507" ht="15" customHeight="1">
       <c r="A507" s="7" t="inlineStr">
@@ -20337,6 +23183,12 @@
       <c r="L507" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M507" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N507" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="508" ht="15" customHeight="1">
       <c r="A508" s="7" t="inlineStr">
@@ -20377,6 +23229,12 @@
       <c r="L508" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M508" s="9" t="n">
+        <v>434</v>
+      </c>
+      <c r="N508" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="509" ht="15" customHeight="1">
       <c r="A509" s="7" t="inlineStr">
@@ -20417,6 +23275,12 @@
       <c r="L509" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M509" s="9" t="n">
+        <v>578</v>
+      </c>
+      <c r="N509" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="510" ht="15" customHeight="1">
       <c r="A510" s="7" t="inlineStr">
@@ -20457,6 +23321,12 @@
       <c r="L510" s="9" t="n">
         <v>6</v>
       </c>
+      <c r="M510" s="9" t="n">
+        <v>118</v>
+      </c>
+      <c r="N510" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="511" ht="15" customHeight="1">
       <c r="A511" s="7" t="inlineStr">
@@ -20497,6 +23367,12 @@
       <c r="L511" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M511" s="9" t="n">
+        <v>942</v>
+      </c>
+      <c r="N511" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="512" ht="15" customHeight="1">
       <c r="A512" s="7" t="inlineStr">
@@ -20537,6 +23413,12 @@
       <c r="L512" s="9" t="n">
         <v>18</v>
       </c>
+      <c r="M512" s="9" t="n">
+        <v>376</v>
+      </c>
+      <c r="N512" s="9" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="513" ht="15" customHeight="1">
       <c r="A513" s="7" t="inlineStr">
@@ -20575,6 +23457,12 @@
         <v>537</v>
       </c>
       <c r="L513" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="M513" s="9" t="n">
+        <v>546</v>
+      </c>
+      <c r="N513" s="9" t="n">
         <v>9</v>
       </c>
     </row>
@@ -20611,6 +23499,12 @@
       <c r="L514" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M514" s="9" t="n">
+        <v>436</v>
+      </c>
+      <c r="N514" s="9" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="515" ht="15" customHeight="1">
       <c r="A515" s="7" t="inlineStr">
@@ -20651,6 +23545,12 @@
       <c r="L515" s="9" t="n">
         <v>9</v>
       </c>
+      <c r="M515" s="9" t="n">
+        <v>626</v>
+      </c>
+      <c r="N515" s="9" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="516" ht="15" customHeight="1">
       <c r="A516" s="7" t="inlineStr">
@@ -20691,6 +23591,12 @@
       <c r="L516" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M516" s="9" t="n">
+        <v>692</v>
+      </c>
+      <c r="N516" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="517" ht="15" customHeight="1">
       <c r="A517" s="7" t="inlineStr">
@@ -20730,6 +23636,12 @@
       </c>
       <c r="L517" s="9" t="n">
         <v>11</v>
+      </c>
+      <c r="M517" s="9" t="n">
+        <v>148</v>
+      </c>
+      <c r="N517" s="9" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="518" ht="15" customHeight="1">
@@ -20760,9 +23672,15 @@
         <v>0</v>
       </c>
       <c r="K518" s="9" t="n">
-        <v>5</v>
+        <v>258</v>
       </c>
       <c r="L518" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="M518" s="9" t="n">
+        <v>260</v>
+      </c>
+      <c r="N518" s="9" t="n">
         <v>5</v>
       </c>
     </row>
@@ -20805,6 +23723,8 @@
       </c>
       <c r="K519" s="9" t="n"/>
       <c r="L519" s="9" t="n"/>
+      <c r="M519" s="9" t="n"/>
+      <c r="N519" s="9" t="n"/>
     </row>
     <row r="520" ht="15" customHeight="1">
       <c r="A520" s="7" t="inlineStr">
@@ -20845,6 +23765,12 @@
       <c r="L520" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M520" s="9" t="n">
+        <v>165</v>
+      </c>
+      <c r="N520" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="521" ht="15" customHeight="1">
       <c r="A521" s="7" t="inlineStr">
@@ -20885,6 +23811,12 @@
       <c r="L521" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M521" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="N521" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="522" ht="15" customHeight="1">
       <c r="A522" s="7" t="inlineStr">
@@ -20925,6 +23857,12 @@
       <c r="L522" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M522" s="9" t="n">
+        <v>667</v>
+      </c>
+      <c r="N522" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="523" ht="15" customHeight="1">
       <c r="A523" s="7" t="inlineStr">
@@ -20965,6 +23903,12 @@
       <c r="L523" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M523" s="9" t="n">
+        <v>113</v>
+      </c>
+      <c r="N523" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="524" ht="15" customHeight="1">
       <c r="A524" s="7" t="inlineStr">
@@ -21005,6 +23949,12 @@
       <c r="L524" s="9" t="n">
         <v>8</v>
       </c>
+      <c r="M524" s="9" t="n">
+        <v>935</v>
+      </c>
+      <c r="N524" s="9" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="525" ht="15" customHeight="1">
       <c r="A525" s="7" t="inlineStr">
@@ -21045,6 +23995,12 @@
       <c r="L525" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M525" s="9" t="n">
+        <v>292</v>
+      </c>
+      <c r="N525" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="526" ht="15" customHeight="1">
       <c r="A526" s="7" t="inlineStr">
@@ -21083,6 +24039,12 @@
         <v>893</v>
       </c>
       <c r="L526" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="M526" s="9" t="n">
+        <v>894</v>
+      </c>
+      <c r="N526" s="9" t="n">
         <v>5</v>
       </c>
     </row>
@@ -21115,6 +24077,8 @@
       <c r="J527" s="9" t="n"/>
       <c r="K527" s="9" t="n"/>
       <c r="L527" s="9" t="n"/>
+      <c r="M527" s="9" t="n"/>
+      <c r="N527" s="9" t="n"/>
     </row>
     <row r="528" ht="15" customHeight="1">
       <c r="A528" s="7" t="inlineStr">
@@ -21155,6 +24119,12 @@
       <c r="L528" s="9" t="n">
         <v>7</v>
       </c>
+      <c r="M528" s="9" t="n">
+        <v>111</v>
+      </c>
+      <c r="N528" s="9" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="529" ht="15" customHeight="1">
       <c r="A529" s="7" t="inlineStr">
@@ -21194,6 +24164,12 @@
       </c>
       <c r="L529" s="9" t="n">
         <v>5</v>
+      </c>
+      <c r="M529" s="9" t="n">
+        <v>1060</v>
+      </c>
+      <c r="N529" s="9" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="530" ht="15" customHeight="1">
@@ -21225,6 +24201,8 @@
       <c r="J530" s="9" t="n"/>
       <c r="K530" s="9" t="n"/>
       <c r="L530" s="9" t="n"/>
+      <c r="M530" s="9" t="n"/>
+      <c r="N530" s="9" t="n"/>
     </row>
     <row r="531" ht="15" customHeight="1">
       <c r="A531" s="7" t="inlineStr">
@@ -21261,6 +24239,12 @@
       <c r="L531" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M531" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N531" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="532" ht="15" customHeight="1">
       <c r="A532" s="7" t="inlineStr">
@@ -21301,6 +24285,12 @@
       <c r="L532" s="9" t="n">
         <v>9</v>
       </c>
+      <c r="M532" s="9" t="n">
+        <v>364</v>
+      </c>
+      <c r="N532" s="9" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="533" ht="15" customHeight="1">
       <c r="A533" s="7" t="inlineStr">
@@ -21341,6 +24331,12 @@
       <c r="L533" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M533" s="9" t="n">
+        <v>375</v>
+      </c>
+      <c r="N533" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="534" ht="15" customHeight="1">
       <c r="A534" s="7" t="inlineStr">
@@ -21381,6 +24377,12 @@
       <c r="L534" s="9" t="n">
         <v>8</v>
       </c>
+      <c r="M534" s="9" t="n">
+        <v>119</v>
+      </c>
+      <c r="N534" s="9" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="535" ht="15" customHeight="1">
       <c r="A535" s="7" t="inlineStr">
@@ -21421,6 +24423,12 @@
       <c r="L535" s="9" t="n">
         <v>6</v>
       </c>
+      <c r="M535" s="9" t="n">
+        <v>292</v>
+      </c>
+      <c r="N535" s="9" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="536" ht="15" customHeight="1">
       <c r="A536" s="7" t="inlineStr">
@@ -21459,6 +24467,12 @@
         <v>856</v>
       </c>
       <c r="L536" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="M536" s="9" t="n">
+        <v>858</v>
+      </c>
+      <c r="N536" s="9" t="n">
         <v>5</v>
       </c>
     </row>
@@ -21491,6 +24505,8 @@
       <c r="J537" s="9" t="n"/>
       <c r="K537" s="9" t="n"/>
       <c r="L537" s="9" t="n"/>
+      <c r="M537" s="9" t="n"/>
+      <c r="N537" s="9" t="n"/>
     </row>
     <row r="538" ht="15" customHeight="1">
       <c r="A538" s="7" t="inlineStr">
@@ -21530,6 +24546,12 @@
       </c>
       <c r="L538" s="9" t="n">
         <v>35</v>
+      </c>
+      <c r="M538" s="9" t="n">
+        <v>1413</v>
+      </c>
+      <c r="N538" s="9" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="539" ht="15" customHeight="1">
@@ -21561,6 +24583,8 @@
       <c r="J539" s="9" t="n"/>
       <c r="K539" s="9" t="n"/>
       <c r="L539" s="9" t="n"/>
+      <c r="M539" s="9" t="n"/>
+      <c r="N539" s="9" t="n"/>
     </row>
     <row r="540" ht="15" customHeight="1">
       <c r="A540" s="7" t="inlineStr">
@@ -21596,9 +24620,15 @@
         <v>6</v>
       </c>
       <c r="K540" s="9" t="n">
-        <v>139</v>
+        <v>370</v>
       </c>
       <c r="L540" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="M540" s="9" t="n">
+        <v>374</v>
+      </c>
+      <c r="N540" s="9" t="n">
         <v>5</v>
       </c>
     </row>
@@ -21641,6 +24671,12 @@
       <c r="L541" s="9" t="n">
         <v>6</v>
       </c>
+      <c r="M541" s="9" t="n">
+        <v>145</v>
+      </c>
+      <c r="N541" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="542" ht="15" customHeight="1">
       <c r="A542" s="7" t="inlineStr">
@@ -21681,6 +24717,12 @@
       <c r="L542" s="9" t="n">
         <v>10</v>
       </c>
+      <c r="M542" s="9" t="n">
+        <v>77</v>
+      </c>
+      <c r="N542" s="9" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="543" ht="15" customHeight="1">
       <c r="A543" s="7" t="inlineStr">
@@ -21721,6 +24763,12 @@
       <c r="L543" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M543" s="9" t="n">
+        <v>140</v>
+      </c>
+      <c r="N543" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="544" ht="15" customHeight="1">
       <c r="A544" s="7" t="inlineStr">
@@ -21761,6 +24809,12 @@
       <c r="L544" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M544" s="9" t="n">
+        <v>1011</v>
+      </c>
+      <c r="N544" s="9" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="545" ht="15" customHeight="1">
       <c r="A545" s="7" t="inlineStr">
@@ -21801,6 +24855,12 @@
       <c r="L545" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M545" s="9" t="n">
+        <v>128</v>
+      </c>
+      <c r="N545" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="546" ht="15" customHeight="1">
       <c r="A546" s="7" t="inlineStr">
@@ -21841,6 +24901,12 @@
       <c r="L546" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M546" s="9" t="n">
+        <v>268</v>
+      </c>
+      <c r="N546" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="547" ht="15" customHeight="1">
       <c r="A547" s="7" t="inlineStr">
@@ -21881,6 +24947,12 @@
       <c r="L547" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M547" s="9" t="n">
+        <v>125</v>
+      </c>
+      <c r="N547" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="548" ht="15" customHeight="1">
       <c r="A548" s="7" t="inlineStr">
@@ -21921,6 +24993,12 @@
       <c r="L548" s="9" t="n">
         <v>6</v>
       </c>
+      <c r="M548" s="9" t="n">
+        <v>646</v>
+      </c>
+      <c r="N548" s="9" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="549" ht="15" customHeight="1">
       <c r="A549" s="7" t="inlineStr">
@@ -21961,6 +25039,12 @@
       <c r="L549" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M549" s="9" t="n">
+        <v>930</v>
+      </c>
+      <c r="N549" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="550" ht="15" customHeight="1">
       <c r="A550" s="7" t="inlineStr">
@@ -22001,6 +25085,12 @@
       <c r="L550" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M550" s="9" t="n">
+        <v>1067</v>
+      </c>
+      <c r="N550" s="9" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="551" ht="15" customHeight="1">
       <c r="A551" s="7" t="inlineStr">
@@ -22040,6 +25130,12 @@
       </c>
       <c r="L551" s="9" t="n">
         <v>5</v>
+      </c>
+      <c r="M551" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="N551" s="9" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="552" ht="15" customHeight="1">
@@ -22071,6 +25167,8 @@
       <c r="J552" s="9" t="n"/>
       <c r="K552" s="9" t="n"/>
       <c r="L552" s="9" t="n"/>
+      <c r="M552" s="9" t="n"/>
+      <c r="N552" s="9" t="n"/>
     </row>
     <row r="553" ht="15" customHeight="1">
       <c r="A553" s="7" t="inlineStr">
@@ -22101,6 +25199,8 @@
       <c r="J553" s="9" t="n"/>
       <c r="K553" s="9" t="n"/>
       <c r="L553" s="9" t="n"/>
+      <c r="M553" s="9" t="n"/>
+      <c r="N553" s="9" t="n"/>
     </row>
     <row r="554" ht="15" customHeight="1">
       <c r="A554" s="7" t="inlineStr">
@@ -22131,6 +25231,8 @@
       <c r="J554" s="9" t="n"/>
       <c r="K554" s="9" t="n"/>
       <c r="L554" s="9" t="n"/>
+      <c r="M554" s="9" t="n"/>
+      <c r="N554" s="9" t="n"/>
     </row>
     <row r="555" ht="15" customHeight="1">
       <c r="A555" s="7" t="inlineStr">
@@ -22161,6 +25263,8 @@
       <c r="J555" s="9" t="n"/>
       <c r="K555" s="9" t="n"/>
       <c r="L555" s="9" t="n"/>
+      <c r="M555" s="9" t="n"/>
+      <c r="N555" s="9" t="n"/>
     </row>
     <row r="556" ht="15" customHeight="1">
       <c r="A556" s="7" t="inlineStr">
@@ -22191,6 +25295,8 @@
       <c r="J556" s="9" t="n"/>
       <c r="K556" s="9" t="n"/>
       <c r="L556" s="9" t="n"/>
+      <c r="M556" s="9" t="n"/>
+      <c r="N556" s="9" t="n"/>
     </row>
     <row r="557" ht="15" customHeight="1">
       <c r="A557" s="7" t="inlineStr">
@@ -22221,6 +25327,8 @@
       <c r="J557" s="9" t="n"/>
       <c r="K557" s="9" t="n"/>
       <c r="L557" s="9" t="n"/>
+      <c r="M557" s="9" t="n"/>
+      <c r="N557" s="9" t="n"/>
     </row>
     <row r="558" ht="15" customHeight="1">
       <c r="A558" s="7" t="inlineStr">
@@ -22251,6 +25359,8 @@
       <c r="J558" s="9" t="n"/>
       <c r="K558" s="9" t="n"/>
       <c r="L558" s="9" t="n"/>
+      <c r="M558" s="9" t="n"/>
+      <c r="N558" s="9" t="n"/>
     </row>
     <row r="559" ht="15" customHeight="1">
       <c r="A559" s="7" t="inlineStr">
@@ -22281,6 +25391,8 @@
       <c r="J559" s="9" t="n"/>
       <c r="K559" s="9" t="n"/>
       <c r="L559" s="9" t="n"/>
+      <c r="M559" s="9" t="n"/>
+      <c r="N559" s="9" t="n"/>
     </row>
     <row r="560" ht="15" customHeight="1">
       <c r="A560" s="7" t="inlineStr">
@@ -22311,6 +25423,8 @@
       <c r="J560" s="9" t="n"/>
       <c r="K560" s="9" t="n"/>
       <c r="L560" s="9" t="n"/>
+      <c r="M560" s="9" t="n"/>
+      <c r="N560" s="9" t="n"/>
     </row>
     <row r="561" ht="15" customHeight="1">
       <c r="A561" s="7" t="inlineStr">
@@ -22341,6 +25455,8 @@
       <c r="J561" s="9" t="n"/>
       <c r="K561" s="9" t="n"/>
       <c r="L561" s="9" t="n"/>
+      <c r="M561" s="9" t="n"/>
+      <c r="N561" s="9" t="n"/>
     </row>
     <row r="562" ht="15" customHeight="1">
       <c r="A562" s="7" t="inlineStr">
@@ -22379,6 +25495,12 @@
         <v>85</v>
       </c>
       <c r="L562" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="M562" s="9" t="n">
+        <v>85</v>
+      </c>
+      <c r="N562" s="9" t="n">
         <v>5</v>
       </c>
     </row>
@@ -22410,9 +25532,15 @@
       <c r="I563" s="9" t="n"/>
       <c r="J563" s="9" t="n"/>
       <c r="K563" s="9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L563" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="M563" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="N563" s="9" t="n">
         <v>5</v>
       </c>
     </row>
@@ -22454,6 +25582,12 @@
       </c>
       <c r="L564" s="9" t="n">
         <v>5</v>
+      </c>
+      <c r="M564" s="9" t="n">
+        <v>387</v>
+      </c>
+      <c r="N564" s="9" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="565" ht="15" customHeight="1">
@@ -22485,6 +25619,8 @@
       <c r="J565" s="9" t="n"/>
       <c r="K565" s="9" t="n"/>
       <c r="L565" s="9" t="n"/>
+      <c r="M565" s="9" t="n"/>
+      <c r="N565" s="9" t="n"/>
     </row>
     <row r="566" ht="15" customHeight="1">
       <c r="A566" s="7" t="inlineStr">
@@ -22525,6 +25661,12 @@
       <c r="L566" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M566" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N566" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="567" ht="15" customHeight="1">
       <c r="A567" s="7" t="inlineStr">
@@ -22565,6 +25707,12 @@
       <c r="L567" s="9" t="n">
         <v>8</v>
       </c>
+      <c r="M567" s="9" t="n">
+        <v>656</v>
+      </c>
+      <c r="N567" s="9" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="568" ht="15" customHeight="1">
       <c r="A568" s="7" t="inlineStr">
@@ -22605,6 +25753,12 @@
       <c r="L568" s="9" t="n">
         <v>7</v>
       </c>
+      <c r="M568" s="9" t="n">
+        <v>329</v>
+      </c>
+      <c r="N568" s="9" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="569" ht="15" customHeight="1">
       <c r="A569" s="7" t="inlineStr">
@@ -22645,6 +25799,12 @@
       <c r="L569" s="9" t="n">
         <v>8</v>
       </c>
+      <c r="M569" s="9" t="n">
+        <v>513</v>
+      </c>
+      <c r="N569" s="9" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="570" ht="15" customHeight="1">
       <c r="A570" s="7" t="inlineStr">
@@ -22683,6 +25843,12 @@
         <v>132</v>
       </c>
       <c r="L570" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="M570" s="9" t="n">
+        <v>132</v>
+      </c>
+      <c r="N570" s="9" t="n">
         <v>5</v>
       </c>
     </row>
@@ -22715,6 +25881,8 @@
       <c r="J571" s="9" t="n"/>
       <c r="K571" s="9" t="n"/>
       <c r="L571" s="9" t="n"/>
+      <c r="M571" s="9" t="n"/>
+      <c r="N571" s="9" t="n"/>
     </row>
     <row r="572" ht="15" customHeight="1">
       <c r="A572" s="7" t="inlineStr">
@@ -22755,6 +25923,12 @@
       <c r="L572" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M572" s="9" t="n">
+        <v>405</v>
+      </c>
+      <c r="N572" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="573" ht="15" customHeight="1">
       <c r="A573" s="7" t="inlineStr">
@@ -22790,9 +25964,15 @@
         <v>10</v>
       </c>
       <c r="K573" s="9" t="n">
-        <v>650</v>
+        <v>745</v>
       </c>
       <c r="L573" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="M573" s="9" t="n">
+        <v>753</v>
+      </c>
+      <c r="N573" s="9" t="n">
         <v>8</v>
       </c>
     </row>
@@ -22833,6 +26013,12 @@
         <v>217</v>
       </c>
       <c r="L574" s="9" t="n"/>
+      <c r="M574" s="9" t="n">
+        <v>217</v>
+      </c>
+      <c r="N574" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="575" ht="15" customHeight="1">
       <c r="A575" s="7" t="inlineStr">
@@ -22871,6 +26057,12 @@
         <v>691</v>
       </c>
       <c r="L575" s="9" t="n"/>
+      <c r="M575" s="9" t="n">
+        <v>700</v>
+      </c>
+      <c r="N575" s="9" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="576" ht="15" customHeight="1">
       <c r="A576" s="7" t="inlineStr">
@@ -22911,6 +26103,10 @@
       <c r="L576" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M576" s="9" t="n">
+        <v>24</v>
+      </c>
+      <c r="N576" s="9" t="n"/>
     </row>
     <row r="577" ht="15" customHeight="1">
       <c r="A577" s="7" t="inlineStr">
@@ -22951,6 +26147,12 @@
       <c r="L577" s="9" t="n">
         <v>7</v>
       </c>
+      <c r="M577" s="9" t="n">
+        <v>231</v>
+      </c>
+      <c r="N577" s="9" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="578" ht="15" customHeight="1">
       <c r="A578" s="7" t="inlineStr">
@@ -22991,15 +26193,22 @@
       <c r="L578" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="M578" s="9" t="n">
+        <v>513</v>
+      </c>
+      <c r="N578" s="9" t="n">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="K1:L1"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="D1:D2"/>
+    <mergeCell ref="M1:N1"/>
     <mergeCell ref="I1:J1"/>
     <mergeCell ref="A1:A2"/>
   </mergeCells>
